--- a/Hoadon/HDVao/11/HDDienTuDaCapMa.xlsx
+++ b/Hoadon/HDVao/11/HDDienTuDaCapMa.xlsx
@@ -314,6 +314,338 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>C25THP</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>13446</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>3502420437</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH TMDV PHƯƠNG HOÀNG</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Số 42D đường 30/4, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="n">
+        <v>3000000.0</v>
+      </c>
+      <c r="L7" s="13" t="n">
+        <v>240000.0</v>
+      </c>
+      <c r="M7" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13" t="n">
+        <v>3240000.0</v>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>C25TBP</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>03/11/2025</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>3502431414</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="n">
+        <v>4000000.0</v>
+      </c>
+      <c r="L8" s="13" t="n">
+        <v>200000.0</v>
+      </c>
+      <c r="M8" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13" t="n">
+        <v>4200000.0</v>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S8" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>C25TBP</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>3502431414</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="n">
+        <v>4450000.0</v>
+      </c>
+      <c r="L9" s="13" t="n">
+        <v>222500.0</v>
+      </c>
+      <c r="M9" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13" t="n">
+        <v>4672500.0</v>
+      </c>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q9" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S9" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>C25TMQ</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>5258</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>08/11/2025</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>3502479416</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THỰC PHẨM MINH QUÂN FOOD</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Số 516 đường Thống Nhất ,Phường Tam Thắng ,Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="n">
+        <v>2770000.0</v>
+      </c>
+      <c r="L10" s="13" t="n">
+        <v>188000.0</v>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13" t="n">
+        <v>2958000.0</v>
+      </c>
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S10" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:S3"/>

--- a/Hoadon/HDVao/11/HDDienTuDaCapMa.xlsx
+++ b/Hoadon/HDVao/11/HDDienTuDaCapMa.xlsx
@@ -408,32 +408,32 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C25TBP</t>
+          <t>C25THP</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>14370</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>3502431414</t>
+          <t>3502420437</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+          <t>CÔNG TY TNHH TMDV PHƯƠNG HOÀNG</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 42D đường 30/4, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
@@ -447,17 +447,17 @@
         </is>
       </c>
       <c r="K8" s="13" t="n">
-        <v>4000000.0</v>
+        <v>1629630.0</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>200000.0</v>
+        <v>130370.0</v>
       </c>
       <c r="M8" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="n">
-        <v>4200000.0</v>
+        <v>1760000.0</v>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
@@ -496,12 +496,12 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>400</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -530,17 +530,17 @@
         </is>
       </c>
       <c r="K9" s="13" t="n">
-        <v>4450000.0</v>
+        <v>4000000.0</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>222500.0</v>
+        <v>200000.0</v>
       </c>
       <c r="M9" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N9" s="13"/>
       <c r="O9" s="13" t="n">
-        <v>4672500.0</v>
+        <v>4200000.0</v>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
@@ -574,32 +574,32 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>C25TMQ</t>
+          <t>C25TBP</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>405</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>08/11/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>3502479416</t>
+          <t>3502431414</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN THỰC PHẨM MINH QUÂN FOOD</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Số 516 đường Thống Nhất ,Phường Tam Thắng ,Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
@@ -613,34 +613,200 @@
         </is>
       </c>
       <c r="K10" s="13" t="n">
-        <v>2770000.0</v>
+        <v>4450000.0</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>188000.0</v>
+        <v>222500.0</v>
       </c>
       <c r="M10" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N10" s="13"/>
       <c r="O10" s="13" t="n">
+        <v>4672500.0</v>
+      </c>
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S10" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>C25TMQ</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>5258</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>08/11/2025</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>3502479416</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THỰC PHẨM MINH QUÂN FOOD</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Số 516 đường Thống Nhất ,Phường Tam Thắng ,Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="n">
+        <v>2770000.0</v>
+      </c>
+      <c r="L11" s="13" t="n">
+        <v>188000.0</v>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13" t="n">
         <v>2958000.0</v>
       </c>
-      <c r="P10" s="7" t="inlineStr">
+      <c r="P11" s="7" t="inlineStr">
         <is>
           <t>VND</t>
         </is>
       </c>
-      <c r="Q10" s="7" t="inlineStr">
+      <c r="Q11" s="7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="R10" s="6" t="inlineStr">
+      <c r="R11" s="6" t="inlineStr">
         <is>
           <t>Hóa đơn mới</t>
         </is>
       </c>
-      <c r="S10" s="6" t="inlineStr">
+      <c r="S11" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>C25THP</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>4285</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>3502550066</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="n">
+        <v>2967371.0</v>
+      </c>
+      <c r="L12" s="13" t="n">
+        <v>237390.0</v>
+      </c>
+      <c r="M12" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13" t="n">
+        <v>3204761.0</v>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
         <is>
           <t>Đã cấp mã hóa đơn</t>
         </is>

--- a/Hoadon/HDVao/11/HDDienTuDaCapMa.xlsx
+++ b/Hoadon/HDVao/11/HDDienTuDaCapMa.xlsx
@@ -657,32 +657,32 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>C25TMQ</t>
+          <t>C25TBP</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>409</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>08/11/2025</t>
+          <t>18/11/2025</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>3502479416</t>
+          <t>3502431414</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN THỰC PHẨM MINH QUÂN FOOD</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Số 516 đường Thống Nhất ,Phường Tam Thắng ,Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
@@ -696,17 +696,17 @@
         </is>
       </c>
       <c r="K11" s="13" t="n">
-        <v>2770000.0</v>
+        <v>4100000.0</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>188000.0</v>
+        <v>205000.0</v>
       </c>
       <c r="M11" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N11" s="13"/>
       <c r="O11" s="13" t="n">
-        <v>2958000.0</v>
+        <v>4305000.0</v>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
@@ -740,32 +740,32 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>C25THP</t>
+          <t>C25TCH</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>4285</t>
+          <t>291</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>3502550066</t>
+          <t>3502470942</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THỰC PHẨM CAO HÂN</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+          <t>142 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
@@ -779,34 +779,198 @@
         </is>
       </c>
       <c r="K12" s="13" t="n">
-        <v>2967371.0</v>
+        <v>4714610.0</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>237390.0</v>
-      </c>
-      <c r="M12" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>235731.0</v>
+      </c>
+      <c r="M12" s="13"/>
       <c r="N12" s="13"/>
       <c r="O12" s="13" t="n">
+        <v>4950341.0</v>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>C25TMQ</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>5258</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>08/11/2025</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>3502479416</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THỰC PHẨM MINH QUÂN FOOD</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Số 516 đường Thống Nhất ,Phường Tam Thắng ,Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>2770000.0</v>
+      </c>
+      <c r="L13" s="13" t="n">
+        <v>188000.0</v>
+      </c>
+      <c r="M13" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13" t="n">
+        <v>2958000.0</v>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>C25THP</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>4285</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>3502550066</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="n">
+        <v>2967371.0</v>
+      </c>
+      <c r="L14" s="13" t="n">
+        <v>237390.0</v>
+      </c>
+      <c r="M14" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13" t="n">
         <v>3204761.0</v>
       </c>
-      <c r="P12" s="7" t="inlineStr">
+      <c r="P14" s="7" t="inlineStr">
         <is>
           <t>VND</t>
         </is>
       </c>
-      <c r="Q12" s="7" t="inlineStr">
+      <c r="Q14" s="7" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="R12" s="6" t="inlineStr">
+      <c r="R14" s="6" t="inlineStr">
         <is>
           <t>Hóa đơn mới</t>
         </is>
       </c>
-      <c r="S12" s="6" t="inlineStr">
+      <c r="S14" s="6" t="inlineStr">
         <is>
           <t>Đã cấp mã hóa đơn</t>
         </is>

--- a/Hoadon/HDVao/11/HDDienTuDaCapMa.xlsx
+++ b/Hoadon/HDVao/11/HDDienTuDaCapMa.xlsx
@@ -325,56 +325,56 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25THP</t>
+          <t>C25TVC</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>13446</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>3502420437</t>
+          <t>0101871229</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH TMDV PHƯƠNG HOÀNG</t>
+          <t>CÔNG TY CỔ PHẦN VCCORP</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Số 42D đường 30/4, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 01, Phố Nguyễn Huy Tưởng, Phường Thanh Xuân, TP.Hà Nội</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>3000000.0</v>
+        <v>2.0E7</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>240000.0</v>
+        <v>1600000.0</v>
       </c>
       <c r="M7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N7" s="13"/>
       <c r="O7" s="13" t="n">
-        <v>3240000.0</v>
+        <v>2.16E7</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -408,56 +408,56 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C25THP</t>
+          <t>C25TDD</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>14370</t>
+          <t>52579</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>01/11/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>3502420437</t>
+          <t>0107581903</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH TMDV PHƯƠNG HOÀNG</t>
+          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM)</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>Số 42D đường 30/4, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Tầng 3, Tòa nhà Lancaster Luminaire, Số 1152-1154 đường Láng, Phường Láng, thành phố Hà Nội</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="K8" s="13" t="n">
-        <v>1629630.0</v>
+        <v>3740741.0</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>130370.0</v>
+        <v>299259.0</v>
       </c>
       <c r="M8" s="13" t="n">
-        <v>0.0</v>
+        <v>300000.0</v>
       </c>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="n">
-        <v>1760000.0</v>
+        <v>4040000.0</v>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
@@ -491,56 +491,56 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C25TBP</t>
+          <t>C25TDD</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>53250</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>3502431414</t>
+          <t>0107581903</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM)</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Tầng 3, Tòa nhà Lancaster Luminaire, Số 1152-1154 đường Láng, Phường Láng, thành phố Hà Nội</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="K9" s="13" t="n">
-        <v>4000000.0</v>
+        <v>3740741.0</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>200000.0</v>
+        <v>299259.0</v>
       </c>
       <c r="M9" s="13" t="n">
-        <v>0.0</v>
+        <v>300000.0</v>
       </c>
       <c r="N9" s="13"/>
       <c r="O9" s="13" t="n">
-        <v>4200000.0</v>
+        <v>4040000.0</v>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
@@ -574,12 +574,12 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>C25TBP</t>
+          <t>C25TDD</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>54228</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -589,41 +589,41 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>3502431414</t>
+          <t>0107581903</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM)</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Tầng 3, Tòa nhà Lancaster Luminaire, Số 1152-1154 đường Láng, Phường Láng, thành phố Hà Nội</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="K10" s="13" t="n">
-        <v>4450000.0</v>
+        <v>3740741.0</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>222500.0</v>
+        <v>299259.0</v>
       </c>
       <c r="M10" s="13" t="n">
-        <v>0.0</v>
+        <v>300000.0</v>
       </c>
       <c r="N10" s="13"/>
       <c r="O10" s="13" t="n">
-        <v>4672500.0</v>
+        <v>4040000.0</v>
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
@@ -657,56 +657,56 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>C25TBP</t>
+          <t>C25TDD</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>54514</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>18/11/2025</t>
+          <t>11/11/2025</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>3502431414</t>
+          <t>0107581903</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ MINH BÁCH PHÁT</t>
+          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM)</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>144C/20 Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Tầng 3, Tòa nhà Lancaster Luminaire, Số 1152-1154 đường Láng, Phường Láng, thành phố Hà Nội</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="K11" s="13" t="n">
-        <v>4100000.0</v>
+        <v>3740741.0</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>205000.0</v>
+        <v>299259.0</v>
       </c>
       <c r="M11" s="13" t="n">
-        <v>0.0</v>
+        <v>300000.0</v>
       </c>
       <c r="N11" s="13"/>
       <c r="O11" s="13" t="n">
-        <v>4305000.0</v>
+        <v>4040000.0</v>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
@@ -740,54 +740,56 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>C25TCH</t>
+          <t>C25TDD</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>55964</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>18/11/2025</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>3502470942</t>
+          <t>0107581903</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THỰC PHẨM CAO HÂN</t>
+          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM)</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>142 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Tầng 3, Tòa nhà Lancaster Luminaire, Số 1152-1154 đường Láng, Phường Láng, thành phố Hà Nội</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="K12" s="13" t="n">
-        <v>4714610.0</v>
+        <v>3740741.0</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>235731.0</v>
-      </c>
-      <c r="M12" s="13"/>
+        <v>299259.0</v>
+      </c>
+      <c r="M12" s="13" t="n">
+        <v>300000.0</v>
+      </c>
       <c r="N12" s="13"/>
       <c r="O12" s="13" t="n">
-        <v>4950341.0</v>
+        <v>4040000.0</v>
       </c>
       <c r="P12" s="7" t="inlineStr">
         <is>
@@ -821,56 +823,56 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>C25TMQ</t>
+          <t>C25TEE</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>08/11/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>3502479416</t>
+          <t>0107581903-001</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN THỰC PHẨM MINH QUÂN FOOD</t>
+          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Số 516 đường Thống Nhất ,Phường Tam Thắng ,Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="K13" s="13" t="n">
-        <v>2770000.0</v>
+        <v>3740741.0</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>188000.0</v>
+        <v>299259.0</v>
       </c>
       <c r="M13" s="13" t="n">
-        <v>0.0</v>
+        <v>300000.0</v>
       </c>
       <c r="N13" s="13"/>
       <c r="O13" s="13" t="n">
-        <v>2958000.0</v>
+        <v>4040000.0</v>
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
@@ -904,56 +906,56 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>C25THP</t>
+          <t>C25TEE</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>4285</t>
+          <t>38652</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>3502550066</t>
+          <t>0107581903-001</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HỒNG PHÁT VŨNG TÀU</t>
+          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>20, Tô Hiến Thành, Phường Vũng Tàu, Thành phố Hồ Chí Minh</t>
+          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502386218</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
         </is>
       </c>
       <c r="K14" s="13" t="n">
-        <v>2967371.0</v>
+        <v>3740741.0</v>
       </c>
       <c r="L14" s="13" t="n">
-        <v>237390.0</v>
+        <v>299259.0</v>
       </c>
       <c r="M14" s="13" t="n">
-        <v>0.0</v>
+        <v>300000.0</v>
       </c>
       <c r="N14" s="13"/>
       <c r="O14" s="13" t="n">
-        <v>3204761.0</v>
+        <v>4040000.0</v>
       </c>
       <c r="P14" s="7" t="inlineStr">
         <is>
@@ -971,6 +973,3355 @@
         </is>
       </c>
       <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>C25TEE</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>39141</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>08/11/2025</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>0107581903-001</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="n">
+        <v>3740741.0</v>
+      </c>
+      <c r="L15" s="13" t="n">
+        <v>299259.0</v>
+      </c>
+      <c r="M15" s="13" t="n">
+        <v>300000.0</v>
+      </c>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13" t="n">
+        <v>4040000.0</v>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>C25TEE</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>39358</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>0107581903-001</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="n">
+        <v>3740741.0</v>
+      </c>
+      <c r="L16" s="13" t="n">
+        <v>299259.0</v>
+      </c>
+      <c r="M16" s="13" t="n">
+        <v>300000.0</v>
+      </c>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13" t="n">
+        <v>4040000.0</v>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>C25TEE</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>39359</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>0107581903-001</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="n">
+        <v>3740741.0</v>
+      </c>
+      <c r="L17" s="13" t="n">
+        <v>299259.0</v>
+      </c>
+      <c r="M17" s="13" t="n">
+        <v>300000.0</v>
+      </c>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13" t="n">
+        <v>4040000.0</v>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S17" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>C25TEE</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>39549</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>11/11/2025</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>0107581903-001</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="n">
+        <v>3740741.0</v>
+      </c>
+      <c r="L18" s="13" t="n">
+        <v>299259.0</v>
+      </c>
+      <c r="M18" s="13" t="n">
+        <v>300000.0</v>
+      </c>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13" t="n">
+        <v>4040000.0</v>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q18" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>C25TEE</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>39550</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>11/11/2025</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>0107581903-001</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="n">
+        <v>3740741.0</v>
+      </c>
+      <c r="L19" s="13" t="n">
+        <v>299259.0</v>
+      </c>
+      <c r="M19" s="13" t="n">
+        <v>300000.0</v>
+      </c>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13" t="n">
+        <v>4040000.0</v>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>C25TEE</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>39551</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>11/11/2025</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>0107581903-001</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="n">
+        <v>3740741.0</v>
+      </c>
+      <c r="L20" s="13" t="n">
+        <v>299259.0</v>
+      </c>
+      <c r="M20" s="13" t="n">
+        <v>300000.0</v>
+      </c>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13" t="n">
+        <v>4040000.0</v>
+      </c>
+      <c r="P20" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q20" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>C25TEE</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>39552</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>11/11/2025</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>0107581903-001</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="n">
+        <v>3740741.0</v>
+      </c>
+      <c r="L21" s="13" t="n">
+        <v>299259.0</v>
+      </c>
+      <c r="M21" s="13" t="n">
+        <v>300000.0</v>
+      </c>
+      <c r="N21" s="13"/>
+      <c r="O21" s="13" t="n">
+        <v>4040000.0</v>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S21" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>C25TEE</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>39793</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>13/11/2025</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>0107581903-001</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="n">
+        <v>3740741.0</v>
+      </c>
+      <c r="L22" s="13" t="n">
+        <v>299259.0</v>
+      </c>
+      <c r="M22" s="13" t="n">
+        <v>300000.0</v>
+      </c>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13" t="n">
+        <v>4040000.0</v>
+      </c>
+      <c r="P22" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q22" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>C25TEE</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>39991</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>15/11/2025</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>0107581903-001</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="n">
+        <v>3740741.0</v>
+      </c>
+      <c r="L23" s="13" t="n">
+        <v>299259.0</v>
+      </c>
+      <c r="M23" s="13" t="n">
+        <v>300000.0</v>
+      </c>
+      <c r="N23" s="13"/>
+      <c r="O23" s="13" t="n">
+        <v>4040000.0</v>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q23" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S23" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>C25TEE</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>40413</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>18/11/2025</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>0107581903-001</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="n">
+        <v>3740741.0</v>
+      </c>
+      <c r="L24" s="13" t="n">
+        <v>299259.0</v>
+      </c>
+      <c r="M24" s="13" t="n">
+        <v>300000.0</v>
+      </c>
+      <c r="N24" s="13"/>
+      <c r="O24" s="13" t="n">
+        <v>4040000.0</v>
+      </c>
+      <c r="P24" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q24" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S24" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>C25TEE</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>40414</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>18/11/2025</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>0107581903-001</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="n">
+        <v>3740741.0</v>
+      </c>
+      <c r="L25" s="13" t="n">
+        <v>299259.0</v>
+      </c>
+      <c r="M25" s="13" t="n">
+        <v>300000.0</v>
+      </c>
+      <c r="N25" s="13"/>
+      <c r="O25" s="13" t="n">
+        <v>4040000.0</v>
+      </c>
+      <c r="P25" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q25" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S25" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>30513</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>04/11/2025</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="n">
+        <v>3695370.0</v>
+      </c>
+      <c r="L26" s="13" t="n">
+        <v>295630.0</v>
+      </c>
+      <c r="M26" s="13"/>
+      <c r="N26" s="13"/>
+      <c r="O26" s="13" t="n">
+        <v>3991000.0</v>
+      </c>
+      <c r="P26" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q26" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S26" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>30514</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>04/11/2025</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="n">
+        <v>3695370.0</v>
+      </c>
+      <c r="L27" s="13" t="n">
+        <v>295630.0</v>
+      </c>
+      <c r="M27" s="13"/>
+      <c r="N27" s="13"/>
+      <c r="O27" s="13" t="n">
+        <v>3991000.0</v>
+      </c>
+      <c r="P27" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q27" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S27" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>30515</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>04/11/2025</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="n">
+        <v>3695370.0</v>
+      </c>
+      <c r="L28" s="13" t="n">
+        <v>295630.0</v>
+      </c>
+      <c r="M28" s="13"/>
+      <c r="N28" s="13"/>
+      <c r="O28" s="13" t="n">
+        <v>3991000.0</v>
+      </c>
+      <c r="P28" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q28" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S28" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>31347</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>11/11/2025</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="n">
+        <v>4032407.0</v>
+      </c>
+      <c r="L29" s="13" t="n">
+        <v>322593.0</v>
+      </c>
+      <c r="M29" s="13"/>
+      <c r="N29" s="13"/>
+      <c r="O29" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P29" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q29" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S29" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>31348</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>11/11/2025</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="n">
+        <v>4032407.0</v>
+      </c>
+      <c r="L30" s="13" t="n">
+        <v>322593.0</v>
+      </c>
+      <c r="M30" s="13"/>
+      <c r="N30" s="13"/>
+      <c r="O30" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P30" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q30" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S30" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>31349</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>11/11/2025</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="n">
+        <v>4032407.0</v>
+      </c>
+      <c r="L31" s="13" t="n">
+        <v>322593.0</v>
+      </c>
+      <c r="M31" s="13"/>
+      <c r="N31" s="13"/>
+      <c r="O31" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P31" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q31" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S31" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>31350</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>11/11/2025</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="n">
+        <v>4032407.0</v>
+      </c>
+      <c r="L32" s="13" t="n">
+        <v>322593.0</v>
+      </c>
+      <c r="M32" s="13"/>
+      <c r="N32" s="13"/>
+      <c r="O32" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P32" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q32" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S32" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>31351</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>11/11/2025</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="n">
+        <v>4032407.0</v>
+      </c>
+      <c r="L33" s="13" t="n">
+        <v>322593.0</v>
+      </c>
+      <c r="M33" s="13"/>
+      <c r="N33" s="13"/>
+      <c r="O33" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P33" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q33" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S33" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>31352</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>11/11/2025</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="n">
+        <v>4032407.0</v>
+      </c>
+      <c r="L34" s="13" t="n">
+        <v>322593.0</v>
+      </c>
+      <c r="M34" s="13"/>
+      <c r="N34" s="13"/>
+      <c r="O34" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P34" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q34" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S34" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>31353</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>11/11/2025</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="n">
+        <v>4032407.0</v>
+      </c>
+      <c r="L35" s="13" t="n">
+        <v>322593.0</v>
+      </c>
+      <c r="M35" s="13"/>
+      <c r="N35" s="13"/>
+      <c r="O35" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P35" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q35" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S35" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>31487</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>12/11/2025</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K36" s="13" t="n">
+        <v>3695370.0</v>
+      </c>
+      <c r="L36" s="13" t="n">
+        <v>295630.0</v>
+      </c>
+      <c r="M36" s="13"/>
+      <c r="N36" s="13"/>
+      <c r="O36" s="13" t="n">
+        <v>3991000.0</v>
+      </c>
+      <c r="P36" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q36" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S36" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>31.0</v>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>31488</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>12/11/2025</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K37" s="13" t="n">
+        <v>3695370.0</v>
+      </c>
+      <c r="L37" s="13" t="n">
+        <v>295630.0</v>
+      </c>
+      <c r="M37" s="13"/>
+      <c r="N37" s="13"/>
+      <c r="O37" s="13" t="n">
+        <v>3991000.0</v>
+      </c>
+      <c r="P37" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q37" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S37" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>31489</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>12/11/2025</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K38" s="13" t="n">
+        <v>3695370.0</v>
+      </c>
+      <c r="L38" s="13" t="n">
+        <v>295630.0</v>
+      </c>
+      <c r="M38" s="13"/>
+      <c r="N38" s="13"/>
+      <c r="O38" s="13" t="n">
+        <v>3991000.0</v>
+      </c>
+      <c r="P38" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q38" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S38" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>33.0</v>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>31670</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K39" s="13" t="n">
+        <v>4032407.0</v>
+      </c>
+      <c r="L39" s="13" t="n">
+        <v>322593.0</v>
+      </c>
+      <c r="M39" s="13"/>
+      <c r="N39" s="13"/>
+      <c r="O39" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P39" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q39" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S39" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>34.0</v>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>31671</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K40" s="13" t="n">
+        <v>4032407.0</v>
+      </c>
+      <c r="L40" s="13" t="n">
+        <v>322593.0</v>
+      </c>
+      <c r="M40" s="13"/>
+      <c r="N40" s="13"/>
+      <c r="O40" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P40" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q40" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S40" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>31672</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K41" s="13" t="n">
+        <v>4032407.0</v>
+      </c>
+      <c r="L41" s="13" t="n">
+        <v>322593.0</v>
+      </c>
+      <c r="M41" s="13"/>
+      <c r="N41" s="13"/>
+      <c r="O41" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P41" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q41" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S41" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>36.0</v>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>31837</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K42" s="13" t="n">
+        <v>4032407.0</v>
+      </c>
+      <c r="L42" s="13" t="n">
+        <v>322593.0</v>
+      </c>
+      <c r="M42" s="13"/>
+      <c r="N42" s="13"/>
+      <c r="O42" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P42" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q42" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S42" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>37.0</v>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>31838</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K43" s="13" t="n">
+        <v>4032407.0</v>
+      </c>
+      <c r="L43" s="13" t="n">
+        <v>322593.0</v>
+      </c>
+      <c r="M43" s="13"/>
+      <c r="N43" s="13"/>
+      <c r="O43" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P43" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q43" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S43" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>38.0</v>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>31839</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K44" s="13" t="n">
+        <v>4032407.0</v>
+      </c>
+      <c r="L44" s="13" t="n">
+        <v>322593.0</v>
+      </c>
+      <c r="M44" s="13"/>
+      <c r="N44" s="13"/>
+      <c r="O44" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P44" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q44" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S44" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n">
+        <v>39.0</v>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>31840</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K45" s="13" t="n">
+        <v>4032407.0</v>
+      </c>
+      <c r="L45" s="13" t="n">
+        <v>322593.0</v>
+      </c>
+      <c r="M45" s="13"/>
+      <c r="N45" s="13"/>
+      <c r="O45" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P45" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q45" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S45" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>31841</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K46" s="13" t="n">
+        <v>4032407.0</v>
+      </c>
+      <c r="L46" s="13" t="n">
+        <v>322593.0</v>
+      </c>
+      <c r="M46" s="13"/>
+      <c r="N46" s="13"/>
+      <c r="O46" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P46" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q46" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S46" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n">
+        <v>41.0</v>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>31842</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K47" s="13" t="n">
+        <v>4032407.0</v>
+      </c>
+      <c r="L47" s="13" t="n">
+        <v>322593.0</v>
+      </c>
+      <c r="M47" s="13"/>
+      <c r="N47" s="13"/>
+      <c r="O47" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P47" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q47" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S47" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>42.0</v>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>31991</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>18/11/2025</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K48" s="13" t="n">
+        <v>4032407.0</v>
+      </c>
+      <c r="L48" s="13" t="n">
+        <v>322593.0</v>
+      </c>
+      <c r="M48" s="13"/>
+      <c r="N48" s="13"/>
+      <c r="O48" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P48" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q48" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S48" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n">
+        <v>43.0</v>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>C25TAB</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>31992</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>18/11/2025</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>0302263527</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K49" s="13" t="n">
+        <v>4032407.0</v>
+      </c>
+      <c r="L49" s="13" t="n">
+        <v>322593.0</v>
+      </c>
+      <c r="M49" s="13"/>
+      <c r="N49" s="13"/>
+      <c r="O49" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P49" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q49" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S49" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>44.0</v>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>C25THB</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>37083</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>11/11/2025</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>0302263527-001</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>Số 28 Phan Bội Châu, Phường Cửa Nam, TP Hà Nội, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I50" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K50" s="13" t="n">
+        <v>4032407.0</v>
+      </c>
+      <c r="L50" s="13" t="n">
+        <v>322593.0</v>
+      </c>
+      <c r="M50" s="13"/>
+      <c r="N50" s="13"/>
+      <c r="O50" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P50" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q50" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S50" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>45.0</v>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>C25TDA</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>11/11/2025</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>0302263527-004</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH CÔNG TY TNHH GIÁO DỤC IDP ( VIỆT NAM) TẠI ĐÀ NẴNG</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>10 NGÔ GIA TỰ, PHƯỜNG HẢI CHÂU, THÀNH PHỐ ĐÀ NẴNG, VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K51" s="13" t="n">
+        <v>4032407.0</v>
+      </c>
+      <c r="L51" s="13" t="n">
+        <v>322593.0</v>
+      </c>
+      <c r="M51" s="13"/>
+      <c r="N51" s="13"/>
+      <c r="O51" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P51" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q51" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S51" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>46.0</v>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>C25TDA</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>7161</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>11/11/2025</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>0302263527-004</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH CÔNG TY TNHH GIÁO DỤC IDP ( VIỆT NAM) TẠI ĐÀ NẴNG</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>10 NGÔ GIA TỰ, PHƯỜNG HẢI CHÂU, THÀNH PHỐ ĐÀ NẴNG, VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="I52" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K52" s="13" t="n">
+        <v>4032407.0</v>
+      </c>
+      <c r="L52" s="13" t="n">
+        <v>322593.0</v>
+      </c>
+      <c r="M52" s="13"/>
+      <c r="N52" s="13"/>
+      <c r="O52" s="13" t="n">
+        <v>4355000.0</v>
+      </c>
+      <c r="P52" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q52" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S52" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>47.0</v>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>C25TAA</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>7087</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>13/11/2025</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>0305412142</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THIẾT BỊ VĂN PHÒNG NHẬT TIẾN THANH</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>176 Lê Hồng Phong, Phường Chợ Quán, TP. Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K53" s="13" t="n">
+        <v>3176900.0</v>
+      </c>
+      <c r="L53" s="13" t="n">
+        <v>254152.0</v>
+      </c>
+      <c r="M53" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N53" s="13"/>
+      <c r="O53" s="13" t="n">
+        <v>3431052.0</v>
+      </c>
+      <c r="P53" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q53" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S53" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>48.0</v>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>C25TPL</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>01/11/2025</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>0309414020</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ XÂY DỰNG PHAN LÊ</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>A-107 Khu nhà ở và nghỉ ngơi giải trí, đường số 5, Phường Tân Hưng, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I54" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K54" s="13" t="n">
+        <v>2.48909091E8</v>
+      </c>
+      <c r="L54" s="13" t="n">
+        <v>2.4890909E7</v>
+      </c>
+      <c r="M54" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N54" s="13"/>
+      <c r="O54" s="13" t="n">
+        <v>2.738E8</v>
+      </c>
+      <c r="P54" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q54" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S54" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="n">
+        <v>49.0</v>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>C25TNB</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>13/11/2025</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>0318332896</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH NƯỚC TÂN BÌNH</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>20 Cộng Hòa, Phường Bảy Hiền, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I55" s="7" t="inlineStr">
+        <is>
+          <t>3502386218</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+        </is>
+      </c>
+      <c r="K55" s="13" t="n">
+        <v>311111.0</v>
+      </c>
+      <c r="L55" s="13" t="n">
+        <v>24889.0</v>
+      </c>
+      <c r="M55" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N55" s="13"/>
+      <c r="O55" s="13" t="n">
+        <v>336000.0</v>
+      </c>
+      <c r="P55" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q55" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S55" s="6" t="inlineStr">
         <is>
           <t>Đã cấp mã hóa đơn</t>
         </is>

--- a/Hoadon/HDVao/11/HDDienTuDaCapMa.xlsx
+++ b/Hoadon/HDVao/11/HDDienTuDaCapMa.xlsx
@@ -325,56 +325,56 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25TMS</t>
+          <t>C25TBN</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>453934</t>
+          <t>5786</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>26/11/2025</t>
+          <t>06/11/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0101243150</t>
+          <t>0107029516</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần MISA</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XUẤT NHẬP KHẨU BÁCH THẮNG</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Tầng 9 Tòa nhà Technosoft, Phố Duy Tân, Phường Cầu Giấy, Thành Phố Hà Nội</t>
+          <t>Tổ 6 Nghĩa Lộ, Phường Yên Nghĩa, Thành phố Hà Nội, Việt Nam</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>1472000.0</v>
+        <v>5890000.0</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>0.0</v>
+        <v>471200.0</v>
       </c>
       <c r="M7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N7" s="13"/>
       <c r="O7" s="13" t="n">
-        <v>1472000.0</v>
+        <v>6361200.0</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -408,56 +408,56 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C25TVC</t>
+          <t>C25TBN</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>7703</t>
+          <t>5857</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>0101871229</t>
+          <t>0107029516</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN VCCORP</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ XUẤT NHẬP KHẨU BÁCH THẮNG</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>Số 01, Phố Nguyễn Huy Tưởng, Phường Thanh Xuân, TP.Hà Nội</t>
+          <t>Tổ 6 Nghĩa Lộ, Phường Yên Nghĩa, Thành phố Hà Nội, Việt Nam</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K8" s="13" t="n">
-        <v>2.0E7</v>
+        <v>1.158E7</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>1600000.0</v>
+        <v>926400.0</v>
       </c>
       <c r="M8" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="n">
-        <v>2.16E7</v>
+        <v>1.25064E7</v>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
@@ -491,56 +491,56 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C25TDD</t>
+          <t>C25TYY</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>52579</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>01/11/2025</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>0107581903</t>
+          <t>0107671314-001</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM)</t>
+          <t>CHI NHÁNH TẠI THÀNH PHỐ HỒ CHÍ MINH - CÔNG TY CỔ PHẦN HOCHIKI VIỆT NAM</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Tầng 3, Tòa nhà Lancaster Luminaire, Số 1152-1154 đường Láng, Phường Láng, thành phố Hà Nội</t>
+          <t>90 đường số 9, Phường An Hội Đông, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K9" s="13" t="n">
-        <v>3740741.0</v>
+        <v>1.504E7</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>299259.0</v>
+        <v>1504000.0</v>
       </c>
       <c r="M9" s="13" t="n">
-        <v>300000.0</v>
+        <v>0.0</v>
       </c>
       <c r="N9" s="13"/>
       <c r="O9" s="13" t="n">
-        <v>4040000.0</v>
+        <v>1.6544E7</v>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
@@ -574,56 +574,56 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>C25TDD</t>
+          <t>C25TAA</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>53250</t>
+          <t>12487</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>0107581903</t>
+          <t>0303427986</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM)</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ VĨNH VĨNH HẰNG</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Tầng 3, Tòa nhà Lancaster Luminaire, Số 1152-1154 đường Láng, Phường Láng, thành phố Hà Nội</t>
+          <t>153 Nguyễn Thông , Phường Nhiêu Lộc, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K10" s="13" t="n">
-        <v>3740741.0</v>
+        <v>1.85E7</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>299259.0</v>
+        <v>1480000.0</v>
       </c>
       <c r="M10" s="13" t="n">
-        <v>300000.0</v>
+        <v>0.0</v>
       </c>
       <c r="N10" s="13"/>
       <c r="O10" s="13" t="n">
-        <v>4040000.0</v>
+        <v>1.998E7</v>
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
@@ -657,56 +657,54 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>C25TDD</t>
+          <t>C25TVE</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>54228</t>
+          <t>9468</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>07/11/2025</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>0107581903</t>
+          <t>0303490096</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM)</t>
+          <t>CÔNG TY CỔ PHẦN TẬP ĐOÀN VNG</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Tầng 3, Tòa nhà Lancaster Luminaire, Số 1152-1154 đường Láng, Phường Láng, thành phố Hà Nội</t>
+          <t>Z06, Đường số 13, Phường Tân Thuận, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K11" s="13" t="n">
-        <v>3740741.0</v>
+        <v>181818.0</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>299259.0</v>
-      </c>
-      <c r="M11" s="13" t="n">
-        <v>300000.0</v>
-      </c>
+        <v>18182.0</v>
+      </c>
+      <c r="M11" s="13"/>
       <c r="N11" s="13"/>
       <c r="O11" s="13" t="n">
-        <v>4040000.0</v>
+        <v>200000.0</v>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
@@ -740,56 +738,54 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>C25TDD</t>
+          <t>C25TDB</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>54514</t>
+          <t>5213</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>06/11/2025</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>0107581903</t>
+          <t>0304117049</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM)</t>
+          <t>CÔNG TY TNHH ĐỒNG BẰNG</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>Tầng 3, Tòa nhà Lancaster Luminaire, Số 1152-1154 đường Láng, Phường Láng, thành phố Hà Nội</t>
+          <t>Cụm công nghiệp Kiến Thành, Ấp 3, Xã Long Cang, Tỉnh Tây Ninh, Việt Nam</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K12" s="13" t="n">
-        <v>3740741.0</v>
+        <v>9205000.0</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>299259.0</v>
-      </c>
-      <c r="M12" s="13" t="n">
-        <v>300000.0</v>
-      </c>
+        <v>736400.0</v>
+      </c>
+      <c r="M12" s="13"/>
       <c r="N12" s="13"/>
       <c r="O12" s="13" t="n">
-        <v>4040000.0</v>
+        <v>9941400.0</v>
       </c>
       <c r="P12" s="7" t="inlineStr">
         <is>
@@ -823,56 +819,56 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>C25TDD</t>
+          <t>C25TYY</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>55964</t>
+          <t>454</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>18/11/2025</t>
+          <t>19/11/2025</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>0107581903</t>
+          <t>0304841558</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM)</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT VĨNH AN</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Tầng 3, Tòa nhà Lancaster Luminaire, Số 1152-1154 đường Láng, Phường Láng, thành phố Hà Nội</t>
+          <t>167/14 Đường D1, Phường Thạnh Mỹ Tây, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K13" s="13" t="n">
-        <v>3740741.0</v>
+        <v>2318000.0</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>299259.0</v>
+        <v>192800.0</v>
       </c>
       <c r="M13" s="13" t="n">
-        <v>300000.0</v>
+        <v>0.0</v>
       </c>
       <c r="N13" s="13"/>
       <c r="O13" s="13" t="n">
-        <v>4040000.0</v>
+        <v>2510800.0</v>
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
@@ -906,56 +902,56 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>C25TEE</t>
+          <t>C25TTD</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>28559</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>07/11/2025</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>0107581903-001</t>
+          <t>0304978344</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
+          <t>Công Ty Cổ Phần Thương Mại Trần Duy</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
+          <t>50 Cầu Xéo, Phường Tân Sơn Nhì, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K14" s="13" t="n">
-        <v>3740741.0</v>
+        <v>5410000.0</v>
       </c>
       <c r="L14" s="13" t="n">
-        <v>299259.0</v>
+        <v>432800.0</v>
       </c>
       <c r="M14" s="13" t="n">
-        <v>300000.0</v>
+        <v>0.0</v>
       </c>
       <c r="N14" s="13"/>
       <c r="O14" s="13" t="n">
-        <v>4040000.0</v>
+        <v>5842800.0</v>
       </c>
       <c r="P14" s="7" t="inlineStr">
         <is>
@@ -989,56 +985,56 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>C25TEE</t>
+          <t>C25TTD</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>38652</t>
+          <t>28949</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>0107581903-001</t>
+          <t>0304978344</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
+          <t>Công Ty Cổ Phần Thương Mại Trần Duy</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
+          <t>50 Cầu Xéo, Phường Tân Sơn Nhì, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K15" s="13" t="n">
-        <v>3740741.0</v>
+        <v>1.038E7</v>
       </c>
       <c r="L15" s="13" t="n">
-        <v>299259.0</v>
+        <v>830400.0</v>
       </c>
       <c r="M15" s="13" t="n">
-        <v>300000.0</v>
+        <v>0.0</v>
       </c>
       <c r="N15" s="13"/>
       <c r="O15" s="13" t="n">
-        <v>4040000.0</v>
+        <v>1.12104E7</v>
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
@@ -1072,56 +1068,56 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>C25TEE</t>
+          <t>C25TTD</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>39141</t>
+          <t>29318</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>08/11/2025</t>
+          <t>18/11/2025</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>0107581903-001</t>
+          <t>0304978344</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
+          <t>Công Ty Cổ Phần Thương Mại Trần Duy</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
+          <t>50 Cầu Xéo, Phường Tân Sơn Nhì, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K16" s="13" t="n">
-        <v>3740741.0</v>
+        <v>7650000.0</v>
       </c>
       <c r="L16" s="13" t="n">
-        <v>299259.0</v>
+        <v>612000.0</v>
       </c>
       <c r="M16" s="13" t="n">
-        <v>300000.0</v>
+        <v>0.0</v>
       </c>
       <c r="N16" s="13"/>
       <c r="O16" s="13" t="n">
-        <v>4040000.0</v>
+        <v>8262000.0</v>
       </c>
       <c r="P16" s="7" t="inlineStr">
         <is>
@@ -1155,56 +1151,56 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>C25TEE</t>
+          <t>C25TYY</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>39358</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>13/11/2025</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>0107581903-001</t>
+          <t>0311259943</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
+          <t>CÔNG TY TNHH THIẾT BỊ ĐIỆN KIM QUANG</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
+          <t>41 Đường số 1, KDC Lý Chiêu Hoàng, Phường An Lạc, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K17" s="13" t="n">
-        <v>3740741.0</v>
+        <v>1.3515921E7</v>
       </c>
       <c r="L17" s="13" t="n">
-        <v>299259.0</v>
+        <v>1081274.0</v>
       </c>
       <c r="M17" s="13" t="n">
-        <v>300000.0</v>
+        <v>0.0</v>
       </c>
       <c r="N17" s="13"/>
       <c r="O17" s="13" t="n">
-        <v>4040000.0</v>
+        <v>1.4597195E7</v>
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
@@ -1238,56 +1234,56 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>C25TEE</t>
+          <t>C25TAM</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>39359</t>
+          <t>563</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>10/11/2025</t>
+          <t>07/11/2025</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>0107581903-001</t>
+          <t>0311735769</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN ANMEC</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
+          <t>14, Đường 27, KDT Vạn Phúc, Phường Hiệp Bình, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K18" s="13" t="n">
-        <v>3740741.0</v>
+        <v>1.6605E7</v>
       </c>
       <c r="L18" s="13" t="n">
-        <v>299259.0</v>
+        <v>1328400.0</v>
       </c>
       <c r="M18" s="13" t="n">
-        <v>300000.0</v>
+        <v>0.0</v>
       </c>
       <c r="N18" s="13"/>
       <c r="O18" s="13" t="n">
-        <v>4040000.0</v>
+        <v>1.79334E7</v>
       </c>
       <c r="P18" s="7" t="inlineStr">
         <is>
@@ -1321,56 +1317,56 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>C25TEE</t>
+          <t>C25TVB</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>39549</t>
+          <t>839</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>18/11/2025</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>0107581903-001</t>
+          <t>0313038474</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
+          <t>CÔNG TY CỔ PHẦN THIẾT BỊ PHÒNG CHÁY VÀ CHỮA CHÁY VIỆT BẢO</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
+          <t>14 Phan Tôn, Phường Tân Định, Tp.Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K19" s="13" t="n">
-        <v>3740741.0</v>
+        <v>432120.0</v>
       </c>
       <c r="L19" s="13" t="n">
-        <v>299259.0</v>
+        <v>34570.0</v>
       </c>
       <c r="M19" s="13" t="n">
-        <v>300000.0</v>
+        <v>0.0</v>
       </c>
       <c r="N19" s="13"/>
       <c r="O19" s="13" t="n">
-        <v>4040000.0</v>
+        <v>466690.0</v>
       </c>
       <c r="P19" s="7" t="inlineStr">
         <is>
@@ -1404,56 +1400,56 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>C25TEE</t>
+          <t>C25TNK</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>39550</t>
+          <t>3567</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>07/11/2025</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>0107581903-001</t>
+          <t>0313573665</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
+          <t>CÔNG TY TNHH ĐẦU TƯ PHÁT TRIỂN CÔNG NGHỆ NIKITA</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
+          <t>761 Quang Trung, Phường An Hội Tây, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K20" s="13" t="n">
-        <v>3740741.0</v>
+        <v>5385500.0</v>
       </c>
       <c r="L20" s="13" t="n">
-        <v>299259.0</v>
+        <v>430840.0</v>
       </c>
       <c r="M20" s="13" t="n">
-        <v>300000.0</v>
+        <v>0.0</v>
       </c>
       <c r="N20" s="13"/>
       <c r="O20" s="13" t="n">
-        <v>4040000.0</v>
+        <v>5816340.0</v>
       </c>
       <c r="P20" s="7" t="inlineStr">
         <is>
@@ -1487,56 +1483,56 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>C25TEE</t>
+          <t>C25TNK</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>39551</t>
+          <t>3759</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>13/11/2025</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>0107581903-001</t>
+          <t>0313573665</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
+          <t>CÔNG TY TNHH ĐẦU TƯ PHÁT TRIỂN CÔNG NGHỆ NIKITA</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
+          <t>761 Quang Trung, Phường An Hội Tây, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K21" s="13" t="n">
-        <v>3740741.0</v>
+        <v>1.7624288E7</v>
       </c>
       <c r="L21" s="13" t="n">
-        <v>299259.0</v>
+        <v>1762429.0</v>
       </c>
       <c r="M21" s="13" t="n">
-        <v>300000.0</v>
+        <v>0.0</v>
       </c>
       <c r="N21" s="13"/>
       <c r="O21" s="13" t="n">
-        <v>4040000.0</v>
+        <v>1.9386717E7</v>
       </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
@@ -1570,56 +1566,56 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>C25TEE</t>
+          <t>C25TNN</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>39552</t>
+          <t>3990</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>07/11/2025</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>0107581903-001</t>
+          <t>0315763164</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
+          <t>CÔNG TY TNHH VẬT TƯ CÔNG NGHIỆP NGUYỄN TRƯƠNG</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
+          <t>Số 818/2 Lê Trọng Tấn, Phường Bình Hưng Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K22" s="13" t="n">
-        <v>3740741.0</v>
+        <v>7937700.0</v>
       </c>
       <c r="L22" s="13" t="n">
-        <v>299259.0</v>
+        <v>775306.0</v>
       </c>
       <c r="M22" s="13" t="n">
-        <v>300000.0</v>
+        <v>0.0</v>
       </c>
       <c r="N22" s="13"/>
       <c r="O22" s="13" t="n">
-        <v>4040000.0</v>
+        <v>8713006.0</v>
       </c>
       <c r="P22" s="7" t="inlineStr">
         <is>
@@ -1653,56 +1649,56 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>C25TEE</t>
+          <t>C25TNN</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>39793</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>13/11/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>0107581903-001</t>
+          <t>0315763164</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
+          <t>CÔNG TY TNHH VẬT TƯ CÔNG NGHIỆP NGUYỄN TRƯƠNG</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
+          <t>Số 818/2 Lê Trọng Tấn, Phường Bình Hưng Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K23" s="13" t="n">
-        <v>3740741.0</v>
+        <v>2408000.0</v>
       </c>
       <c r="L23" s="13" t="n">
-        <v>299259.0</v>
+        <v>219800.0</v>
       </c>
       <c r="M23" s="13" t="n">
-        <v>300000.0</v>
+        <v>0.0</v>
       </c>
       <c r="N23" s="13"/>
       <c r="O23" s="13" t="n">
-        <v>4040000.0</v>
+        <v>2627800.0</v>
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
@@ -1736,56 +1732,56 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>C25TEE</t>
+          <t>C25TTB</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>39991</t>
+          <t>1726</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>15/11/2025</t>
+          <t>26/11/2025</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>0107581903-001</t>
+          <t>0315945911</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÚC THIÊN BẢO</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
+          <t>289 Bến Bình Đông, Phường Phú Định, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K24" s="13" t="n">
-        <v>3740741.0</v>
+        <v>1.35E7</v>
       </c>
       <c r="L24" s="13" t="n">
-        <v>299259.0</v>
+        <v>1080000.0</v>
       </c>
       <c r="M24" s="13" t="n">
-        <v>300000.0</v>
+        <v>0.0</v>
       </c>
       <c r="N24" s="13"/>
       <c r="O24" s="13" t="n">
-        <v>4040000.0</v>
+        <v>1.458E7</v>
       </c>
       <c r="P24" s="7" t="inlineStr">
         <is>
@@ -1819,56 +1815,56 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>C25TEE</t>
+          <t>C25TYY</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>40413</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>18/11/2025</t>
+          <t>07/11/2025</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>0107581903-001</t>
+          <t>0316298086</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
+          <t>CÔNG TY TNHH IN ẤN KHẮC DẤU AN AN</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
+          <t>337 Xô Viết Nghệ Tĩnh , Phường Bình Thạnh , TP. Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K25" s="13" t="n">
-        <v>3740741.0</v>
+        <v>310000.0</v>
       </c>
       <c r="L25" s="13" t="n">
-        <v>299259.0</v>
+        <v>24800.0</v>
       </c>
       <c r="M25" s="13" t="n">
-        <v>300000.0</v>
+        <v>0.0</v>
       </c>
       <c r="N25" s="13"/>
       <c r="O25" s="13" t="n">
-        <v>4040000.0</v>
+        <v>334800.0</v>
       </c>
       <c r="P25" s="7" t="inlineStr">
         <is>
@@ -1902,56 +1898,56 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>C25TEE</t>
+          <t>C25TTH</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>40414</t>
+          <t>371</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>18/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>0107581903-001</t>
+          <t>0316302945</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI CƠ KHÍ THANH HẢI</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
+          <t>65/8B Ấp Vạn Hạnh, Xã Bà Điểm, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH TM DV PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K26" s="13" t="n">
-        <v>3740741.0</v>
+        <v>3200000.0</v>
       </c>
       <c r="L26" s="13" t="n">
-        <v>299259.0</v>
+        <v>256000.0</v>
       </c>
       <c r="M26" s="13" t="n">
-        <v>300000.0</v>
+        <v>0.0</v>
       </c>
       <c r="N26" s="13"/>
       <c r="O26" s="13" t="n">
-        <v>4040000.0</v>
+        <v>3456000.0</v>
       </c>
       <c r="P26" s="7" t="inlineStr">
         <is>
@@ -1985,56 +1981,56 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>C25TEE</t>
+          <t>C25TAE</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>40618</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>26/11/2025</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>0107581903-001</t>
+          <t>0319238568</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
+          <t>TRUNG TÂM DỊCH VỤ PHÂN TÍCH THÍ NGHIỆM VÀ TIÊU CHUẨN ĐO LƯỜNG CHẤT LƯỢNG THÀNH PHỐ HỒ CHÍ MINH</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
+          <t>Số 2 Nguyễn Văn Thủ, Phường Tân Định, TP Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K27" s="13" t="n">
-        <v>3740741.0</v>
+        <v>500000.0</v>
       </c>
       <c r="L27" s="13" t="n">
-        <v>299259.0</v>
+        <v>25000.0</v>
       </c>
       <c r="M27" s="13" t="n">
-        <v>300000.0</v>
+        <v>0.0</v>
       </c>
       <c r="N27" s="13"/>
       <c r="O27" s="13" t="n">
-        <v>4040000.0</v>
+        <v>525000.0</v>
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
@@ -2068,56 +2064,56 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>C25TEE</t>
+          <t>C25TYY</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>40750</t>
+          <t>1821</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>0107581903-001</t>
+          <t>0700801090</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
+          <t>CÔNG TY TNHH S-TEC VINA</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
+          <t>Lô CN-03, Khu công nghiệp Đồng Văn IV, Phường Lê Hồ, Tỉnh Ninh Bình</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K28" s="13" t="n">
-        <v>3740741.0</v>
+        <v>1950000.0</v>
       </c>
       <c r="L28" s="13" t="n">
-        <v>299259.0</v>
+        <v>156000.0</v>
       </c>
       <c r="M28" s="13" t="n">
-        <v>300000.0</v>
+        <v>0.0</v>
       </c>
       <c r="N28" s="13"/>
       <c r="O28" s="13" t="n">
-        <v>4040000.0</v>
+        <v>2106000.0</v>
       </c>
       <c r="P28" s="7" t="inlineStr">
         <is>
@@ -2146,61 +2142,57 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>C25TEE</t>
+          <t>C25TTH</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>41076</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>0107581903-001</t>
+          <t>077082010300</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
+          <t>HỘ KINH DOANH NGUYỄN TẤN HÙNG</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
+          <t>393 đường Thống Nhất, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
-        </is>
-      </c>
-      <c r="K29" s="13" t="n">
-        <v>3740741.0</v>
-      </c>
-      <c r="L29" s="13" t="n">
-        <v>299259.0</v>
-      </c>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+        </is>
+      </c>
+      <c r="K29" s="13"/>
+      <c r="L29" s="13"/>
       <c r="M29" s="13" t="n">
-        <v>300000.0</v>
+        <v>0.0</v>
       </c>
       <c r="N29" s="13"/>
       <c r="O29" s="13" t="n">
-        <v>4040000.0</v>
+        <v>300000.0</v>
       </c>
       <c r="P29" s="7" t="inlineStr">
         <is>
@@ -2229,61 +2221,55 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>C25TEE</t>
+          <t>C25TAD</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>41077</t>
+          <t>657</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>13/11/2025</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>0107581903-001</t>
+          <t>3500182201</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
+          <t>TRẦN MINH LUÂN( ANH ĐÀO MEN)</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
+          <t>134, Bạch Đằng, Phường Bà Rịa, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
-        </is>
-      </c>
-      <c r="K30" s="13" t="n">
-        <v>3740741.0</v>
-      </c>
-      <c r="L30" s="13" t="n">
-        <v>299259.0</v>
-      </c>
-      <c r="M30" s="13" t="n">
-        <v>300000.0</v>
-      </c>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+        </is>
+      </c>
+      <c r="K30" s="13"/>
+      <c r="L30" s="13"/>
+      <c r="M30" s="13"/>
       <c r="N30" s="13"/>
       <c r="O30" s="13" t="n">
-        <v>4040000.0</v>
+        <v>520000.0</v>
       </c>
       <c r="P30" s="7" t="inlineStr">
         <is>
@@ -2317,56 +2303,54 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>C25TEE</t>
+          <t>C25THT</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>41078</t>
+          <t>4241</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>0107581903-001</t>
+          <t>3500422189</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN HUỲNH TẤN</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
+          <t>Số 11 Huyền Trân Công Chúa, Phường Tam thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K31" s="13" t="n">
-        <v>3740741.0</v>
+        <v>1.4685185E7</v>
       </c>
       <c r="L31" s="13" t="n">
-        <v>299259.0</v>
-      </c>
-      <c r="M31" s="13" t="n">
-        <v>300000.0</v>
-      </c>
+        <v>1174815.0</v>
+      </c>
+      <c r="M31" s="13"/>
       <c r="N31" s="13"/>
       <c r="O31" s="13" t="n">
-        <v>4040000.0</v>
+        <v>1.586E7</v>
       </c>
       <c r="P31" s="7" t="inlineStr">
         <is>
@@ -2400,56 +2384,54 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>C25TEE</t>
+          <t>C25THT</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>41095</t>
+          <t>4272</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>0107581903-001</t>
+          <t>3500422189</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN HUỲNH TẤN</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
+          <t>Số 11 Huyền Trân Công Chúa, Phường Tam thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K32" s="13" t="n">
-        <v>3740741.0</v>
+        <v>1111111.0</v>
       </c>
       <c r="L32" s="13" t="n">
-        <v>299259.0</v>
-      </c>
-      <c r="M32" s="13" t="n">
-        <v>300000.0</v>
-      </c>
+        <v>88889.0</v>
+      </c>
+      <c r="M32" s="13"/>
       <c r="N32" s="13"/>
       <c r="O32" s="13" t="n">
-        <v>4040000.0</v>
+        <v>1200000.0</v>
       </c>
       <c r="P32" s="7" t="inlineStr">
         <is>
@@ -2483,56 +2465,56 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>C25TEE</t>
+          <t>C25THP</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>41096</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>0107581903-001</t>
+          <t>3500730546</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
+          <t>CÔNG TY TNHH SẢN XUẤT THƯƠNG MẠI VÀ DỊCH VỤ HÒA PHÁT</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
+          <t>149 Huyền Trân Công Chúa, Phường Tam Thắng, TP. Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>Công Ty TNHH Thương Mại Dịch Vụ Phòng Cháy Chữa Cháy Minh Hoàng</t>
         </is>
       </c>
       <c r="K33" s="13" t="n">
-        <v>3740741.0</v>
+        <v>1500027.0</v>
       </c>
       <c r="L33" s="13" t="n">
-        <v>299259.0</v>
+        <v>150003.0</v>
       </c>
       <c r="M33" s="13" t="n">
-        <v>300000.0</v>
+        <v>0.0</v>
       </c>
       <c r="N33" s="13"/>
       <c r="O33" s="13" t="n">
-        <v>4040000.0</v>
+        <v>1650030.0</v>
       </c>
       <c r="P33" s="7" t="inlineStr">
         <is>
@@ -2566,56 +2548,56 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>C25TEE</t>
+          <t>C25THP</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>41097</t>
+          <t>1366</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>08/11/2025</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>0107581903-001</t>
+          <t>3500730546</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
+          <t>CÔNG TY TNHH SẢN XUẤT THƯƠNG MẠI VÀ DỊCH VỤ HÒA PHÁT</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
+          <t>149 Huyền Trân Công Chúa, Phường Tam Thắng, TP. Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>Công Ty TNHH Thương Mại Dịch Vụ Phòng Cháy Chữa Cháy Minh Hoàng</t>
         </is>
       </c>
       <c r="K34" s="13" t="n">
-        <v>3740741.0</v>
+        <v>501818.0</v>
       </c>
       <c r="L34" s="13" t="n">
-        <v>299259.0</v>
+        <v>50182.0</v>
       </c>
       <c r="M34" s="13" t="n">
-        <v>300000.0</v>
+        <v>0.0</v>
       </c>
       <c r="N34" s="13"/>
       <c r="O34" s="13" t="n">
-        <v>4040000.0</v>
+        <v>552000.0</v>
       </c>
       <c r="P34" s="7" t="inlineStr">
         <is>
@@ -2649,12 +2631,12 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>C25TEE</t>
+          <t>C25THP</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>41371</t>
+          <t>1486</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
@@ -2664,41 +2646,41 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>0107581903-001</t>
+          <t>3500730546</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
+          <t>CÔNG TY TNHH SẢN XUẤT THƯƠNG MẠI VÀ DỊCH VỤ HÒA PHÁT</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
+          <t>149 Huyền Trân Công Chúa, Phường Tam Thắng, TP. Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>Công Ty TNHH Thương Mại Dịch Vụ Phòng Cháy Chữa Cháy Minh Hoàng</t>
         </is>
       </c>
       <c r="K35" s="13" t="n">
-        <v>3740741.0</v>
+        <v>9.1877716E7</v>
       </c>
       <c r="L35" s="13" t="n">
-        <v>299259.0</v>
+        <v>9187772.0</v>
       </c>
       <c r="M35" s="13" t="n">
-        <v>300000.0</v>
+        <v>0.0</v>
       </c>
       <c r="N35" s="13"/>
       <c r="O35" s="13" t="n">
-        <v>4040000.0</v>
+        <v>1.01065488E8</v>
       </c>
       <c r="P35" s="7" t="inlineStr">
         <is>
@@ -2732,56 +2714,56 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>C25TEE</t>
+          <t>C25TAA</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>41372</t>
+          <t>25948</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>26/11/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>0107581903-001</t>
+          <t>3500780339</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BRITISH COUNCIL (VIỆT NAM) - CHI NHÁNH TP.HCM</t>
+          <t>CÔNG TY CỔ PHẦN VŨNG TÀU TRƯỜNG HẢI</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>285 Cách Mạng Tháng Tám, Phường Hòa Hưng, Thành phố Hồ Chí Minh</t>
+          <t>Quốc lộ 51, Phường Bà Rịa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>Công Ty TNHH Thương Mại Dịch Vụ Phòng Cháy Chữa Cháy Minh Hoàng</t>
         </is>
       </c>
       <c r="K36" s="13" t="n">
-        <v>3740741.0</v>
+        <v>1882828.0</v>
       </c>
       <c r="L36" s="13" t="n">
-        <v>299259.0</v>
+        <v>150626.0</v>
       </c>
       <c r="M36" s="13" t="n">
-        <v>300000.0</v>
+        <v>0.0</v>
       </c>
       <c r="N36" s="13"/>
       <c r="O36" s="13" t="n">
-        <v>4040000.0</v>
+        <v>2033454.0</v>
       </c>
       <c r="P36" s="7" t="inlineStr">
         <is>
@@ -2815,54 +2797,56 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TKA</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>30513</t>
+          <t>3550</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>26/11/2025</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>3502234945</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ NGỌC KỲ ANH</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 636 Trần Phú, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K37" s="13" t="n">
-        <v>3695370.0</v>
+        <v>2007300.0</v>
       </c>
       <c r="L37" s="13" t="n">
-        <v>295630.0</v>
-      </c>
-      <c r="M37" s="13"/>
+        <v>160584.0</v>
+      </c>
+      <c r="M37" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N37" s="13"/>
       <c r="O37" s="13" t="n">
-        <v>3991000.0</v>
+        <v>2167884.0</v>
       </c>
       <c r="P37" s="7" t="inlineStr">
         <is>
@@ -2896,54 +2880,56 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TYZ</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>30514</t>
+          <t>1399</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>3502244950</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN IN ẤN VÀ QUẢNG CÁO NGỌC HIẾU</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>281 Nguyễn An Ninh, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I38" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K38" s="13" t="n">
-        <v>3695370.0</v>
+        <v>3700000.0</v>
       </c>
       <c r="L38" s="13" t="n">
-        <v>295630.0</v>
-      </c>
-      <c r="M38" s="13"/>
+        <v>296000.0</v>
+      </c>
+      <c r="M38" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N38" s="13"/>
       <c r="O38" s="13" t="n">
-        <v>3991000.0</v>
+        <v>3996000.0</v>
       </c>
       <c r="P38" s="7" t="inlineStr">
         <is>
@@ -2977,54 +2963,54 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TPD</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>30515</t>
+          <t>42</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>26/11/2025</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>3502345451</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ AN TOÀN PCCC PHƯƠNG ĐÔNG</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>D15 Ông Ích Khiêm, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K39" s="13" t="n">
-        <v>3695370.0</v>
+        <v>3.0E8</v>
       </c>
       <c r="L39" s="13" t="n">
-        <v>295630.0</v>
+        <v>2.4E7</v>
       </c>
       <c r="M39" s="13"/>
       <c r="N39" s="13"/>
       <c r="O39" s="13" t="n">
-        <v>3991000.0</v>
+        <v>3.24E8</v>
       </c>
       <c r="P39" s="7" t="inlineStr">
         <is>
@@ -3058,54 +3044,56 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TTP</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>31347</t>
+          <t>711</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>3502391909</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ TÂN LONG PHƯỚC</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 9 Hà Huy Tập, đường D5 khu Biệt Thự Thanh Bình, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K40" s="13" t="n">
-        <v>4032407.0</v>
+        <v>1018520.0</v>
       </c>
       <c r="L40" s="13" t="n">
-        <v>322593.0</v>
-      </c>
-      <c r="M40" s="13"/>
+        <v>81482.0</v>
+      </c>
+      <c r="M40" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N40" s="13"/>
       <c r="O40" s="13" t="n">
-        <v>4355000.0</v>
+        <v>1100002.0</v>
       </c>
       <c r="P40" s="7" t="inlineStr">
         <is>
@@ -3139,54 +3127,56 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TTP</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>31348</t>
+          <t>743</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>3502391909</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ TÂN LONG PHƯỚC</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 9 Hà Huy Tập, đường D5 khu Biệt Thự Thanh Bình, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K41" s="13" t="n">
-        <v>4032407.0</v>
+        <v>2.7498508E7</v>
       </c>
       <c r="L41" s="13" t="n">
-        <v>322593.0</v>
-      </c>
-      <c r="M41" s="13"/>
+        <v>2199881.0</v>
+      </c>
+      <c r="M41" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N41" s="13"/>
       <c r="O41" s="13" t="n">
-        <v>4355000.0</v>
+        <v>2.9698389E7</v>
       </c>
       <c r="P41" s="7" t="inlineStr">
         <is>
@@ -3220,54 +3210,56 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TTP</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>31349</t>
+          <t>107</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>3502410862</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY TNHH THY PHƯƠNG THỊNH</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Tổ 11, Ấp Tân Lễ B, Xã Châu Pha, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K42" s="13" t="n">
-        <v>4032407.0</v>
+        <v>1103793.0</v>
       </c>
       <c r="L42" s="13" t="n">
-        <v>322593.0</v>
-      </c>
-      <c r="M42" s="13"/>
+        <v>96207.0</v>
+      </c>
+      <c r="M42" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N42" s="13"/>
       <c r="O42" s="13" t="n">
-        <v>4355000.0</v>
+        <v>1200000.0</v>
       </c>
       <c r="P42" s="7" t="inlineStr">
         <is>
@@ -3301,54 +3293,56 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TVT</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>31350</t>
+          <t>843</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>3502414810</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY TNHH KHÍ LONG SƠN</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Thôn 1, Xã Long Sơn, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K43" s="13" t="n">
-        <v>4032407.0</v>
+        <v>2100000.0</v>
       </c>
       <c r="L43" s="13" t="n">
-        <v>322593.0</v>
-      </c>
-      <c r="M43" s="13"/>
+        <v>168000.0</v>
+      </c>
+      <c r="M43" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N43" s="13"/>
       <c r="O43" s="13" t="n">
-        <v>4355000.0</v>
+        <v>2268000.0</v>
       </c>
       <c r="P43" s="7" t="inlineStr">
         <is>
@@ -3382,54 +3376,54 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25THD</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>31351</t>
+          <t>156</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>3502469665</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY TNHH TM DV KỸ THUẬT Ô TÔ HOÀNG DŨNG</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 1, Đường Lê Hồng Phong, phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I44" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K44" s="13" t="n">
-        <v>4032407.0</v>
+        <v>2500000.0</v>
       </c>
       <c r="L44" s="13" t="n">
-        <v>322593.0</v>
+        <v>200000.0</v>
       </c>
       <c r="M44" s="13"/>
       <c r="N44" s="13"/>
       <c r="O44" s="13" t="n">
-        <v>4355000.0</v>
+        <v>2700000.0</v>
       </c>
       <c r="P44" s="7" t="inlineStr">
         <is>
@@ -3463,54 +3457,54 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TLT</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>31352</t>
+          <t>41050</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>01/11/2025</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>3600718503</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ KINH DOANH GOLF LONG THÀNH</t>
         </is>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 99A, đường Phước Tân - Long Hưng, Phường Phước Tân, Tỉnh Đồng Nai, Việt Nam</t>
         </is>
       </c>
       <c r="I45" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K45" s="13" t="n">
-        <v>4032407.0</v>
+        <v>717593.0</v>
       </c>
       <c r="L45" s="13" t="n">
-        <v>322593.0</v>
+        <v>57407.0</v>
       </c>
       <c r="M45" s="13"/>
       <c r="N45" s="13"/>
       <c r="O45" s="13" t="n">
-        <v>4355000.0</v>
+        <v>775000.0</v>
       </c>
       <c r="P45" s="7" t="inlineStr">
         <is>
@@ -3544,54 +3538,54 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TLT</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>31353</t>
+          <t>41051</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>01/11/2025</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>3600718503</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ KINH DOANH GOLF LONG THÀNH</t>
         </is>
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 99A, đường Phước Tân - Long Hưng, Phường Phước Tân, Tỉnh Đồng Nai, Việt Nam</t>
         </is>
       </c>
       <c r="I46" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K46" s="13" t="n">
-        <v>4032407.0</v>
+        <v>381818.0</v>
       </c>
       <c r="L46" s="13" t="n">
-        <v>322593.0</v>
+        <v>38182.0</v>
       </c>
       <c r="M46" s="13"/>
       <c r="N46" s="13"/>
       <c r="O46" s="13" t="n">
-        <v>4355000.0</v>
+        <v>420000.0</v>
       </c>
       <c r="P46" s="7" t="inlineStr">
         <is>
@@ -3625,54 +3619,54 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TLT</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>31487</t>
+          <t>41052</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>01/11/2025</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>3600718503</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ KINH DOANH GOLF LONG THÀNH</t>
         </is>
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 99A, đường Phước Tân - Long Hưng, Phường Phước Tân, Tỉnh Đồng Nai, Việt Nam</t>
         </is>
       </c>
       <c r="I47" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K47" s="13" t="n">
-        <v>3695370.0</v>
+        <v>884259.0</v>
       </c>
       <c r="L47" s="13" t="n">
-        <v>295630.0</v>
+        <v>70741.0</v>
       </c>
       <c r="M47" s="13"/>
       <c r="N47" s="13"/>
       <c r="O47" s="13" t="n">
-        <v>3991000.0</v>
+        <v>955000.0</v>
       </c>
       <c r="P47" s="7" t="inlineStr">
         <is>
@@ -3706,54 +3700,54 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TLT</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>31488</t>
+          <t>41053</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>01/11/2025</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>3600718503</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ KINH DOANH GOLF LONG THÀNH</t>
         </is>
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 99A, đường Phước Tân - Long Hưng, Phường Phước Tân, Tỉnh Đồng Nai, Việt Nam</t>
         </is>
       </c>
       <c r="I48" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K48" s="13" t="n">
-        <v>3695370.0</v>
+        <v>1240909.0</v>
       </c>
       <c r="L48" s="13" t="n">
-        <v>295630.0</v>
+        <v>124091.0</v>
       </c>
       <c r="M48" s="13"/>
       <c r="N48" s="13"/>
       <c r="O48" s="13" t="n">
-        <v>3991000.0</v>
+        <v>1365000.0</v>
       </c>
       <c r="P48" s="7" t="inlineStr">
         <is>
@@ -3787,54 +3781,54 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TLT</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>31489</t>
+          <t>41288</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>02/11/2025</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>3600718503</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ KINH DOANH GOLF LONG THÀNH</t>
         </is>
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 99A, đường Phước Tân - Long Hưng, Phường Phước Tân, Tỉnh Đồng Nai, Việt Nam</t>
         </is>
       </c>
       <c r="I49" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K49" s="13" t="n">
-        <v>3695370.0</v>
+        <v>831481.0</v>
       </c>
       <c r="L49" s="13" t="n">
-        <v>295630.0</v>
+        <v>66519.0</v>
       </c>
       <c r="M49" s="13"/>
       <c r="N49" s="13"/>
       <c r="O49" s="13" t="n">
-        <v>3991000.0</v>
+        <v>898000.0</v>
       </c>
       <c r="P49" s="7" t="inlineStr">
         <is>
@@ -3868,54 +3862,54 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TLT</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>31670</t>
+          <t>41289</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>02/11/2025</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>3600718503</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ KINH DOANH GOLF LONG THÀNH</t>
         </is>
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 99A, đường Phước Tân - Long Hưng, Phường Phước Tân, Tỉnh Đồng Nai, Việt Nam</t>
         </is>
       </c>
       <c r="I50" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J50" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K50" s="13" t="n">
-        <v>4032407.0</v>
+        <v>327273.0</v>
       </c>
       <c r="L50" s="13" t="n">
-        <v>322593.0</v>
+        <v>32727.0</v>
       </c>
       <c r="M50" s="13"/>
       <c r="N50" s="13"/>
       <c r="O50" s="13" t="n">
-        <v>4355000.0</v>
+        <v>360000.0</v>
       </c>
       <c r="P50" s="7" t="inlineStr">
         <is>
@@ -3949,54 +3943,54 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TLT</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>31671</t>
+          <t>41290</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>02/11/2025</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>3600718503</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ KINH DOANH GOLF LONG THÀNH</t>
         </is>
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 99A, đường Phước Tân - Long Hưng, Phường Phước Tân, Tỉnh Đồng Nai, Việt Nam</t>
         </is>
       </c>
       <c r="I51" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K51" s="13" t="n">
-        <v>4032407.0</v>
+        <v>1402778.0</v>
       </c>
       <c r="L51" s="13" t="n">
-        <v>322593.0</v>
+        <v>112222.0</v>
       </c>
       <c r="M51" s="13"/>
       <c r="N51" s="13"/>
       <c r="O51" s="13" t="n">
-        <v>4355000.0</v>
+        <v>1515000.0</v>
       </c>
       <c r="P51" s="7" t="inlineStr">
         <is>
@@ -4030,54 +4024,54 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TLT</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>31672</t>
+          <t>41291</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>02/11/2025</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>3600718503</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ KINH DOANH GOLF LONG THÀNH</t>
         </is>
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 99A, đường Phước Tân - Long Hưng, Phường Phước Tân, Tỉnh Đồng Nai, Việt Nam</t>
         </is>
       </c>
       <c r="I52" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K52" s="13" t="n">
-        <v>4032407.0</v>
+        <v>1131818.0</v>
       </c>
       <c r="L52" s="13" t="n">
-        <v>322593.0</v>
+        <v>113182.0</v>
       </c>
       <c r="M52" s="13"/>
       <c r="N52" s="13"/>
       <c r="O52" s="13" t="n">
-        <v>4355000.0</v>
+        <v>1245000.0</v>
       </c>
       <c r="P52" s="7" t="inlineStr">
         <is>
@@ -4111,54 +4105,54 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TLT</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>31837</t>
+          <t>41417</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>3600718503</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ KINH DOANH GOLF LONG THÀNH</t>
         </is>
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 99A, đường Phước Tân - Long Hưng, Phường Phước Tân, Tỉnh Đồng Nai, Việt Nam</t>
         </is>
       </c>
       <c r="I53" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K53" s="13" t="n">
-        <v>4032407.0</v>
+        <v>1179630.0</v>
       </c>
       <c r="L53" s="13" t="n">
-        <v>322593.0</v>
+        <v>94370.0</v>
       </c>
       <c r="M53" s="13"/>
       <c r="N53" s="13"/>
       <c r="O53" s="13" t="n">
-        <v>4355000.0</v>
+        <v>1274000.0</v>
       </c>
       <c r="P53" s="7" t="inlineStr">
         <is>
@@ -4192,54 +4186,54 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TLT</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>31838</t>
+          <t>41418</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>3600718503</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ KINH DOANH GOLF LONG THÀNH</t>
         </is>
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 99A, đường Phước Tân - Long Hưng, Phường Phước Tân, Tỉnh Đồng Nai, Việt Nam</t>
         </is>
       </c>
       <c r="I54" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K54" s="13" t="n">
-        <v>4032407.0</v>
+        <v>545455.0</v>
       </c>
       <c r="L54" s="13" t="n">
-        <v>322593.0</v>
+        <v>54545.0</v>
       </c>
       <c r="M54" s="13"/>
       <c r="N54" s="13"/>
       <c r="O54" s="13" t="n">
-        <v>4355000.0</v>
+        <v>600000.0</v>
       </c>
       <c r="P54" s="7" t="inlineStr">
         <is>
@@ -4273,54 +4267,54 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TLT</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>31839</t>
+          <t>41419</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>3600718503</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ KINH DOANH GOLF LONG THÀNH</t>
         </is>
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 99A, đường Phước Tân - Long Hưng, Phường Phước Tân, Tỉnh Đồng Nai, Việt Nam</t>
         </is>
       </c>
       <c r="I55" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K55" s="13" t="n">
-        <v>4032407.0</v>
+        <v>346296.0</v>
       </c>
       <c r="L55" s="13" t="n">
-        <v>322593.0</v>
+        <v>27704.0</v>
       </c>
       <c r="M55" s="13"/>
       <c r="N55" s="13"/>
       <c r="O55" s="13" t="n">
-        <v>4355000.0</v>
+        <v>374000.0</v>
       </c>
       <c r="P55" s="7" t="inlineStr">
         <is>
@@ -4354,54 +4348,54 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TLT</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>31840</t>
+          <t>41789</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>06/11/2025</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>3600718503</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ KINH DOANH GOLF LONG THÀNH</t>
         </is>
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 99A, đường Phước Tân - Long Hưng, Phường Phước Tân, Tỉnh Đồng Nai, Việt Nam</t>
         </is>
       </c>
       <c r="I56" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J56" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K56" s="13" t="n">
-        <v>4032407.0</v>
+        <v>863636.0</v>
       </c>
       <c r="L56" s="13" t="n">
-        <v>322593.0</v>
+        <v>86364.0</v>
       </c>
       <c r="M56" s="13"/>
       <c r="N56" s="13"/>
       <c r="O56" s="13" t="n">
-        <v>4355000.0</v>
+        <v>950000.0</v>
       </c>
       <c r="P56" s="7" t="inlineStr">
         <is>
@@ -4435,54 +4429,54 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TLT</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>31841</t>
+          <t>41790</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>06/11/2025</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>3600718503</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ KINH DOANH GOLF LONG THÀNH</t>
         </is>
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 99A, đường Phước Tân - Long Hưng, Phường Phước Tân, Tỉnh Đồng Nai, Việt Nam</t>
         </is>
       </c>
       <c r="I57" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K57" s="13" t="n">
-        <v>4032407.0</v>
+        <v>669444.0</v>
       </c>
       <c r="L57" s="13" t="n">
-        <v>322593.0</v>
+        <v>53556.0</v>
       </c>
       <c r="M57" s="13"/>
       <c r="N57" s="13"/>
       <c r="O57" s="13" t="n">
-        <v>4355000.0</v>
+        <v>723000.0</v>
       </c>
       <c r="P57" s="7" t="inlineStr">
         <is>
@@ -4516,54 +4510,54 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TLT</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>31842</t>
+          <t>41791</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>17/11/2025</t>
+          <t>06/11/2025</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>3600718503</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ KINH DOANH GOLF LONG THÀNH</t>
         </is>
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 99A, đường Phước Tân - Long Hưng, Phường Phước Tân, Tỉnh Đồng Nai, Việt Nam</t>
         </is>
       </c>
       <c r="I58" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J58" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K58" s="13" t="n">
-        <v>4032407.0</v>
+        <v>490909.0</v>
       </c>
       <c r="L58" s="13" t="n">
-        <v>322593.0</v>
+        <v>49091.0</v>
       </c>
       <c r="M58" s="13"/>
       <c r="N58" s="13"/>
       <c r="O58" s="13" t="n">
-        <v>4355000.0</v>
+        <v>540000.0</v>
       </c>
       <c r="P58" s="7" t="inlineStr">
         <is>
@@ -4597,54 +4591,54 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TLT</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>31991</t>
+          <t>41792</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>18/11/2025</t>
+          <t>06/11/2025</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>3600718503</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ KINH DOANH GOLF LONG THÀNH</t>
         </is>
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 99A, đường Phước Tân - Long Hưng, Phường Phước Tân, Tỉnh Đồng Nai, Việt Nam</t>
         </is>
       </c>
       <c r="I59" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K59" s="13" t="n">
-        <v>4032407.0</v>
+        <v>2082870.0</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>322593.0</v>
+        <v>166630.0</v>
       </c>
       <c r="M59" s="13"/>
       <c r="N59" s="13"/>
       <c r="O59" s="13" t="n">
-        <v>4355000.0</v>
+        <v>2249500.0</v>
       </c>
       <c r="P59" s="7" t="inlineStr">
         <is>
@@ -4678,54 +4672,54 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TLT</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>31992</t>
+          <t>41793</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>18/11/2025</t>
+          <t>06/11/2025</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>3600718503</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ KINH DOANH GOLF LONG THÀNH</t>
         </is>
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 99A, đường Phước Tân - Long Hưng, Phường Phước Tân, Tỉnh Đồng Nai, Việt Nam</t>
         </is>
       </c>
       <c r="I60" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K60" s="13" t="n">
-        <v>4032407.0</v>
+        <v>163636.0</v>
       </c>
       <c r="L60" s="13" t="n">
-        <v>322593.0</v>
+        <v>16364.0</v>
       </c>
       <c r="M60" s="13"/>
       <c r="N60" s="13"/>
       <c r="O60" s="13" t="n">
-        <v>4355000.0</v>
+        <v>180000.0</v>
       </c>
       <c r="P60" s="7" t="inlineStr">
         <is>
@@ -4759,54 +4753,54 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TLT</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>32201</t>
+          <t>41962</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>07/11/2025</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>3600718503</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ KINH DOANH GOLF LONG THÀNH</t>
         </is>
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 99A, đường Phước Tân - Long Hưng, Phường Phước Tân, Tỉnh Đồng Nai, Việt Nam</t>
         </is>
       </c>
       <c r="I61" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K61" s="13" t="n">
-        <v>4032407.0</v>
+        <v>671296.0</v>
       </c>
       <c r="L61" s="13" t="n">
-        <v>322593.0</v>
+        <v>53704.0</v>
       </c>
       <c r="M61" s="13"/>
       <c r="N61" s="13"/>
       <c r="O61" s="13" t="n">
-        <v>4355000.0</v>
+        <v>725000.0</v>
       </c>
       <c r="P61" s="7" t="inlineStr">
         <is>
@@ -4840,54 +4834,54 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TLT</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>32202</t>
+          <t>41963</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>07/11/2025</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>3600718503</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ KINH DOANH GOLF LONG THÀNH</t>
         </is>
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 99A, đường Phước Tân - Long Hưng, Phường Phước Tân, Tỉnh Đồng Nai, Việt Nam</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J62" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K62" s="13" t="n">
-        <v>4032407.0</v>
+        <v>1690909.0</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>322593.0</v>
+        <v>169091.0</v>
       </c>
       <c r="M62" s="13"/>
       <c r="N62" s="13"/>
       <c r="O62" s="13" t="n">
-        <v>4355000.0</v>
+        <v>1860000.0</v>
       </c>
       <c r="P62" s="7" t="inlineStr">
         <is>
@@ -4921,54 +4915,54 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TLT</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>32203</t>
+          <t>41964</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>07/11/2025</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>3600718503</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ KINH DOANH GOLF LONG THÀNH</t>
         </is>
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 99A, đường Phước Tân - Long Hưng, Phường Phước Tân, Tỉnh Đồng Nai, Việt Nam</t>
         </is>
       </c>
       <c r="I63" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K63" s="13" t="n">
-        <v>4032407.0</v>
+        <v>1801852.0</v>
       </c>
       <c r="L63" s="13" t="n">
-        <v>322593.0</v>
+        <v>144148.0</v>
       </c>
       <c r="M63" s="13"/>
       <c r="N63" s="13"/>
       <c r="O63" s="13" t="n">
-        <v>4355000.0</v>
+        <v>1946000.0</v>
       </c>
       <c r="P63" s="7" t="inlineStr">
         <is>
@@ -5002,54 +4996,54 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TLT</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>32452</t>
+          <t>42378</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>3600718503</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ KINH DOANH GOLF LONG THÀNH</t>
         </is>
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 99A, đường Phước Tân - Long Hưng, Phường Phước Tân, Tỉnh Đồng Nai, Việt Nam</t>
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J64" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K64" s="13" t="n">
-        <v>4032407.0</v>
+        <v>1831818.0</v>
       </c>
       <c r="L64" s="13" t="n">
-        <v>322593.0</v>
+        <v>183182.0</v>
       </c>
       <c r="M64" s="13"/>
       <c r="N64" s="13"/>
       <c r="O64" s="13" t="n">
-        <v>4355000.0</v>
+        <v>2015000.0</v>
       </c>
       <c r="P64" s="7" t="inlineStr">
         <is>
@@ -5083,54 +5077,54 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TLT</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>32453</t>
+          <t>42379</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>3600718503</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ KINH DOANH GOLF LONG THÀNH</t>
         </is>
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 99A, đường Phước Tân - Long Hưng, Phường Phước Tân, Tỉnh Đồng Nai, Việt Nam</t>
         </is>
       </c>
       <c r="I65" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K65" s="13" t="n">
-        <v>4032407.0</v>
+        <v>398148.0</v>
       </c>
       <c r="L65" s="13" t="n">
-        <v>322593.0</v>
+        <v>31852.0</v>
       </c>
       <c r="M65" s="13"/>
       <c r="N65" s="13"/>
       <c r="O65" s="13" t="n">
-        <v>4355000.0</v>
+        <v>430000.0</v>
       </c>
       <c r="P65" s="7" t="inlineStr">
         <is>
@@ -5164,54 +5158,54 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TLT</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>32454</t>
+          <t>42380</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>3600718503</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ KINH DOANH GOLF LONG THÀNH</t>
         </is>
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 99A, đường Phước Tân - Long Hưng, Phường Phước Tân, Tỉnh Đồng Nai, Việt Nam</t>
         </is>
       </c>
       <c r="I66" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J66" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K66" s="13" t="n">
-        <v>4032407.0</v>
+        <v>709091.0</v>
       </c>
       <c r="L66" s="13" t="n">
-        <v>322593.0</v>
+        <v>70909.0</v>
       </c>
       <c r="M66" s="13"/>
       <c r="N66" s="13"/>
       <c r="O66" s="13" t="n">
-        <v>4355000.0</v>
+        <v>780000.0</v>
       </c>
       <c r="P66" s="7" t="inlineStr">
         <is>
@@ -5245,54 +5239,54 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TLT</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>32455</t>
+          <t>42381</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>10/11/2025</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>3600718503</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ KINH DOANH GOLF LONG THÀNH</t>
         </is>
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 99A, đường Phước Tân - Long Hưng, Phường Phước Tân, Tỉnh Đồng Nai, Việt Nam</t>
         </is>
       </c>
       <c r="I67" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K67" s="13" t="n">
-        <v>4032407.0</v>
+        <v>1150926.0</v>
       </c>
       <c r="L67" s="13" t="n">
-        <v>322593.0</v>
+        <v>92074.0</v>
       </c>
       <c r="M67" s="13"/>
       <c r="N67" s="13"/>
       <c r="O67" s="13" t="n">
-        <v>4355000.0</v>
+        <v>1243000.0</v>
       </c>
       <c r="P67" s="7" t="inlineStr">
         <is>
@@ -5326,54 +5320,54 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TLT</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>32472</t>
+          <t>43198</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>15/11/2025</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>3600718503</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ KINH DOANH GOLF LONG THÀNH</t>
         </is>
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 99A, đường Phước Tân - Long Hưng, Phường Phước Tân, Tỉnh Đồng Nai, Việt Nam</t>
         </is>
       </c>
       <c r="I68" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J68" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K68" s="13" t="n">
-        <v>4032407.0</v>
+        <v>3582407.0</v>
       </c>
       <c r="L68" s="13" t="n">
-        <v>322593.0</v>
+        <v>286593.0</v>
       </c>
       <c r="M68" s="13"/>
       <c r="N68" s="13"/>
       <c r="O68" s="13" t="n">
-        <v>4355000.0</v>
+        <v>3869000.0</v>
       </c>
       <c r="P68" s="7" t="inlineStr">
         <is>
@@ -5407,54 +5401,54 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>C25TAB</t>
+          <t>C25TLT</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>32473</t>
+          <t>43199</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>15/11/2025</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>3600718503</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ KINH DOANH GOLF LONG THÀNH</t>
         </is>
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 99A, đường Phước Tân - Long Hưng, Phường Phước Tân, Tỉnh Đồng Nai, Việt Nam</t>
         </is>
       </c>
       <c r="I69" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K69" s="13" t="n">
-        <v>4032407.0</v>
+        <v>109091.0</v>
       </c>
       <c r="L69" s="13" t="n">
-        <v>322593.0</v>
+        <v>10909.0</v>
       </c>
       <c r="M69" s="13"/>
       <c r="N69" s="13"/>
       <c r="O69" s="13" t="n">
-        <v>4355000.0</v>
+        <v>120000.0</v>
       </c>
       <c r="P69" s="7" t="inlineStr">
         <is>
@@ -5488,54 +5482,54 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>C25TAD</t>
+          <t>C25TLT</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>2742</t>
+          <t>43342</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>16/11/2025</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>3600718503</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ KINH DOANH GOLF LONG THÀNH</t>
         </is>
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 99A, đường Phước Tân - Long Hưng, Phường Phước Tân, Tỉnh Đồng Nai, Việt Nam</t>
         </is>
       </c>
       <c r="I70" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J70" s="6" t="inlineStr">
         <is>
-          <t>Công Ty TNHH The Forum Education Vietnam</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K70" s="13" t="n">
-        <v>2.3194689E7</v>
+        <v>591667.0</v>
       </c>
       <c r="L70" s="13" t="n">
-        <v>1855575.0</v>
+        <v>47333.0</v>
       </c>
       <c r="M70" s="13"/>
       <c r="N70" s="13"/>
       <c r="O70" s="13" t="n">
-        <v>2.5050264E7</v>
+        <v>639000.0</v>
       </c>
       <c r="P70" s="7" t="inlineStr">
         <is>
@@ -5569,54 +5563,54 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>C25TAD</t>
+          <t>C25TLT</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>2743</t>
+          <t>43343</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>16/11/2025</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>0302263527</t>
+          <t>3600718503</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ KINH DOANH GOLF LONG THÀNH</t>
         </is>
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>161-161A Hai Bà Trưng, Phường Xuân Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 99A, đường Phước Tân - Long Hưng, Phường Phước Tân, Tỉnh Đồng Nai, Việt Nam</t>
         </is>
       </c>
       <c r="I71" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>Công Ty TNHH The Forum Education Vietnam</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K71" s="13" t="n">
-        <v>1325925.0</v>
+        <v>981818.0</v>
       </c>
       <c r="L71" s="13" t="n">
-        <v>66296.0</v>
+        <v>98182.0</v>
       </c>
       <c r="M71" s="13"/>
       <c r="N71" s="13"/>
       <c r="O71" s="13" t="n">
-        <v>1392221.0</v>
+        <v>1080000.0</v>
       </c>
       <c r="P71" s="7" t="inlineStr">
         <is>
@@ -5650,54 +5644,54 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>C25THB</t>
+          <t>C25TLT</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>37083</t>
+          <t>43344</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>16/11/2025</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>0302263527-001</t>
+          <t>3600718503</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH GIÁO DỤC IDP (VIỆT NAM)</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ KINH DOANH GOLF LONG THÀNH</t>
         </is>
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>Số 28 Phan Bội Châu, Phường Cửa Nam, TP Hà Nội, Việt Nam</t>
+          <t>Số 99A, đường Phước Tân - Long Hưng, Phường Phước Tân, Tỉnh Đồng Nai, Việt Nam</t>
         </is>
       </c>
       <c r="I72" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J72" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K72" s="13" t="n">
-        <v>4032407.0</v>
+        <v>1698426.0</v>
       </c>
       <c r="L72" s="13" t="n">
-        <v>322593.0</v>
+        <v>135874.0</v>
       </c>
       <c r="M72" s="13"/>
       <c r="N72" s="13"/>
       <c r="O72" s="13" t="n">
-        <v>4355000.0</v>
+        <v>1834300.0</v>
       </c>
       <c r="P72" s="7" t="inlineStr">
         <is>
@@ -5731,54 +5725,54 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>C25TDA</t>
+          <t>C25TLT</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>43345</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>16/11/2025</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>0302263527-004</t>
+          <t>3600718503</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH GIÁO DỤC IDP ( VIỆT NAM) TẠI ĐÀ NẴNG</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ KINH DOANH GOLF LONG THÀNH</t>
         </is>
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>10 NGÔ GIA TỰ, PHƯỜNG HẢI CHÂU, THÀNH PHỐ ĐÀ NẴNG, VIỆT NAM</t>
+          <t>Số 99A, đường Phước Tân - Long Hưng, Phường Phước Tân, Tỉnh Đồng Nai, Việt Nam</t>
         </is>
       </c>
       <c r="I73" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K73" s="13" t="n">
-        <v>4032407.0</v>
+        <v>863636.0</v>
       </c>
       <c r="L73" s="13" t="n">
-        <v>322593.0</v>
+        <v>86364.0</v>
       </c>
       <c r="M73" s="13"/>
       <c r="N73" s="13"/>
       <c r="O73" s="13" t="n">
-        <v>4355000.0</v>
+        <v>950000.0</v>
       </c>
       <c r="P73" s="7" t="inlineStr">
         <is>
@@ -5812,54 +5806,54 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>C25TDA</t>
+          <t>C25TLT</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>43707</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>11/11/2025</t>
+          <t>18/11/2025</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>0302263527-004</t>
+          <t>3600718503</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH GIÁO DỤC IDP ( VIỆT NAM) TẠI ĐÀ NẴNG</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ KINH DOANH GOLF LONG THÀNH</t>
         </is>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>10 NGÔ GIA TỰ, PHƯỜNG HẢI CHÂU, THÀNH PHỐ ĐÀ NẴNG, VIỆT NAM</t>
+          <t>Số 99A, đường Phước Tân - Long Hưng, Phường Phước Tân, Tỉnh Đồng Nai, Việt Nam</t>
         </is>
       </c>
       <c r="I74" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J74" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K74" s="13" t="n">
-        <v>4032407.0</v>
+        <v>3014815.0</v>
       </c>
       <c r="L74" s="13" t="n">
-        <v>322593.0</v>
+        <v>241185.0</v>
       </c>
       <c r="M74" s="13"/>
       <c r="N74" s="13"/>
       <c r="O74" s="13" t="n">
-        <v>4355000.0</v>
+        <v>3256000.0</v>
       </c>
       <c r="P74" s="7" t="inlineStr">
         <is>
@@ -5893,56 +5887,54 @@
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>C25TAA</t>
+          <t>C25TLT</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>7087</t>
+          <t>43708</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>13/11/2025</t>
+          <t>18/11/2025</t>
         </is>
       </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>0305412142</t>
+          <t>3600718503</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THIẾT BỊ VĂN PHÒNG NHẬT TIẾN THANH</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ KINH DOANH GOLF LONG THÀNH</t>
         </is>
       </c>
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>176 Lê Hồng Phong, Phường Chợ Quán, TP. Hồ Chí Minh, Việt Nam</t>
+          <t>Số 99A, đường Phước Tân - Long Hưng, Phường Phước Tân, Tỉnh Đồng Nai, Việt Nam</t>
         </is>
       </c>
       <c r="I75" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K75" s="13" t="n">
-        <v>3176900.0</v>
+        <v>777273.0</v>
       </c>
       <c r="L75" s="13" t="n">
-        <v>254152.0</v>
-      </c>
-      <c r="M75" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>77727.0</v>
+      </c>
+      <c r="M75" s="13"/>
       <c r="N75" s="13"/>
       <c r="O75" s="13" t="n">
-        <v>3431052.0</v>
+        <v>855000.0</v>
       </c>
       <c r="P75" s="7" t="inlineStr">
         <is>
@@ -5976,56 +5968,54 @@
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>C25TPL</t>
+          <t>C25TLT</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>44087</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>01/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
-          <t>0309414020</t>
+          <t>3600718503</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ XÂY DỰNG PHAN LÊ</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ KINH DOANH GOLF LONG THÀNH</t>
         </is>
       </c>
       <c r="H76" s="6" t="inlineStr">
         <is>
-          <t>A-107 Khu nhà ở và nghỉ ngơi giải trí, đường số 5, Phường Tân Hưng, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Số 99A, đường Phước Tân - Long Hưng, Phường Phước Tân, Tỉnh Đồng Nai, Việt Nam</t>
         </is>
       </c>
       <c r="I76" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J76" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K76" s="13" t="n">
-        <v>2.48909091E8</v>
+        <v>49091.0</v>
       </c>
       <c r="L76" s="13" t="n">
-        <v>2.4890909E7</v>
-      </c>
-      <c r="M76" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>4909.0</v>
+      </c>
+      <c r="M76" s="13"/>
       <c r="N76" s="13"/>
       <c r="O76" s="13" t="n">
-        <v>2.738E8</v>
+        <v>54000.0</v>
       </c>
       <c r="P76" s="7" t="inlineStr">
         <is>
@@ -6059,56 +6049,54 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>C25TBP</t>
+          <t>C25TLT</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>44088</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>26/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>0311567151</t>
+          <t>3600718503</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH DỊCH VỤ VỆ SINH BÌNH PHƯƠNG</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ KINH DOANH GOLF LONG THÀNH</t>
         </is>
       </c>
       <c r="H77" s="6" t="inlineStr">
         <is>
-          <t>22/47A Tân Hóa, Phường Minh Phụng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 99A, đường Phước Tân - Long Hưng, Phường Phước Tân, Tỉnh Đồng Nai, Việt Nam</t>
         </is>
       </c>
       <c r="I77" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K77" s="13" t="n">
-        <v>1.1608846E7</v>
+        <v>3312407.0</v>
       </c>
       <c r="L77" s="13" t="n">
-        <v>928708.0</v>
-      </c>
-      <c r="M77" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>264993.0</v>
+      </c>
+      <c r="M77" s="13"/>
       <c r="N77" s="13"/>
       <c r="O77" s="13" t="n">
-        <v>1.2537554E7</v>
+        <v>3577400.0</v>
       </c>
       <c r="P77" s="7" t="inlineStr">
         <is>
@@ -6142,56 +6130,54 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>C25TNB</t>
+          <t>C25TLT</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>44487</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>13/11/2025</t>
+          <t>22/11/2025</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>0318332896</t>
+          <t>3600718503</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH NƯỚC TÂN BÌNH</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ KINH DOANH GOLF LONG THÀNH</t>
         </is>
       </c>
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>20 Cộng Hòa, Phường Bảy Hiền, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 99A, đường Phước Tân - Long Hưng, Phường Phước Tân, Tỉnh Đồng Nai, Việt Nam</t>
         </is>
       </c>
       <c r="I78" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J78" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K78" s="13" t="n">
-        <v>311111.0</v>
+        <v>1848148.0</v>
       </c>
       <c r="L78" s="13" t="n">
-        <v>24889.0</v>
-      </c>
-      <c r="M78" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>147852.0</v>
+      </c>
+      <c r="M78" s="13"/>
       <c r="N78" s="13"/>
       <c r="O78" s="13" t="n">
-        <v>336000.0</v>
+        <v>1996000.0</v>
       </c>
       <c r="P78" s="7" t="inlineStr">
         <is>
@@ -6225,56 +6211,54 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>C25TYY</t>
+          <t>C25TLT</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>5063</t>
+          <t>44490</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>22/11/2025</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>3502413292</t>
+          <t>3600718503</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐÀO TẠO HANEX</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ KINH DOANH GOLF LONG THÀNH</t>
         </is>
       </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>85 Nguyễn Thái Học, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 99A, đường Phước Tân - Long Hưng, Phường Phước Tân, Tỉnh Đồng Nai, Việt Nam</t>
         </is>
       </c>
       <c r="I79" s="7" t="inlineStr">
         <is>
-          <t>3502386218</t>
+          <t>3501972322</t>
         </is>
       </c>
       <c r="J79" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THE FORUM EDUCATION VIETNAM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
         </is>
       </c>
       <c r="K79" s="13" t="n">
-        <v>1275462.0</v>
+        <v>272727.0</v>
       </c>
       <c r="L79" s="13" t="n">
-        <v>102038.0</v>
-      </c>
-      <c r="M79" s="13" t="n">
-        <v>67130.0</v>
-      </c>
+        <v>27273.0</v>
+      </c>
+      <c r="M79" s="13"/>
       <c r="N79" s="13"/>
       <c r="O79" s="13" t="n">
-        <v>1377500.0</v>
+        <v>300000.0</v>
       </c>
       <c r="P79" s="7" t="inlineStr">
         <is>
@@ -6292,6 +6276,905 @@
         </is>
       </c>
       <c r="S79" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="n">
+        <v>74.0</v>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>C25TLT</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>44492</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>22/11/2025</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>3600718503</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ KINH DOANH GOLF LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>Số 99A, đường Phước Tân - Long Hưng, Phường Phước Tân, Tỉnh Đồng Nai, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I80" s="7" t="inlineStr">
+        <is>
+          <t>3501972322</t>
+        </is>
+      </c>
+      <c r="J80" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+        </is>
+      </c>
+      <c r="K80" s="13" t="n">
+        <v>2453704.0</v>
+      </c>
+      <c r="L80" s="13" t="n">
+        <v>196296.0</v>
+      </c>
+      <c r="M80" s="13"/>
+      <c r="N80" s="13"/>
+      <c r="O80" s="13" t="n">
+        <v>2650000.0</v>
+      </c>
+      <c r="P80" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q80" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R80" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S80" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="n">
+        <v>75.0</v>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>C25TLT</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>44557</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>23/11/2025</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>3600718503</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ KINH DOANH GOLF LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>Số 99A, đường Phước Tân - Long Hưng, Phường Phước Tân, Tỉnh Đồng Nai, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I81" s="7" t="inlineStr">
+        <is>
+          <t>3501972322</t>
+        </is>
+      </c>
+      <c r="J81" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+        </is>
+      </c>
+      <c r="K81" s="13" t="n">
+        <v>1333333.0</v>
+      </c>
+      <c r="L81" s="13" t="n">
+        <v>106667.0</v>
+      </c>
+      <c r="M81" s="13"/>
+      <c r="N81" s="13"/>
+      <c r="O81" s="13" t="n">
+        <v>1440000.0</v>
+      </c>
+      <c r="P81" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q81" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R81" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S81" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="n">
+        <v>76.0</v>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>C25TLT</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>44558</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>23/11/2025</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>3600718503</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ KINH DOANH GOLF LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t>Số 99A, đường Phước Tân - Long Hưng, Phường Phước Tân, Tỉnh Đồng Nai, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I82" s="7" t="inlineStr">
+        <is>
+          <t>3501972322</t>
+        </is>
+      </c>
+      <c r="J82" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+        </is>
+      </c>
+      <c r="K82" s="13" t="n">
+        <v>109091.0</v>
+      </c>
+      <c r="L82" s="13" t="n">
+        <v>10909.0</v>
+      </c>
+      <c r="M82" s="13"/>
+      <c r="N82" s="13"/>
+      <c r="O82" s="13" t="n">
+        <v>120000.0</v>
+      </c>
+      <c r="P82" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q82" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R82" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S82" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="n">
+        <v>77.0</v>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>C25TLT</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>44559</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>23/11/2025</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t>3600718503</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ KINH DOANH GOLF LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H83" s="6" t="inlineStr">
+        <is>
+          <t>Số 99A, đường Phước Tân - Long Hưng, Phường Phước Tân, Tỉnh Đồng Nai, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I83" s="7" t="inlineStr">
+        <is>
+          <t>3501972322</t>
+        </is>
+      </c>
+      <c r="J83" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+        </is>
+      </c>
+      <c r="K83" s="13" t="n">
+        <v>2282407.0</v>
+      </c>
+      <c r="L83" s="13" t="n">
+        <v>182593.0</v>
+      </c>
+      <c r="M83" s="13"/>
+      <c r="N83" s="13"/>
+      <c r="O83" s="13" t="n">
+        <v>2465000.0</v>
+      </c>
+      <c r="P83" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q83" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R83" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S83" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="n">
+        <v>78.0</v>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>C25TLT</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>44560</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>23/11/2025</t>
+        </is>
+      </c>
+      <c r="F84" s="7" t="inlineStr">
+        <is>
+          <t>3600718503</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ KINH DOANH GOLF LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H84" s="6" t="inlineStr">
+        <is>
+          <t>Số 99A, đường Phước Tân - Long Hưng, Phường Phước Tân, Tỉnh Đồng Nai, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I84" s="7" t="inlineStr">
+        <is>
+          <t>3501972322</t>
+        </is>
+      </c>
+      <c r="J84" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+        </is>
+      </c>
+      <c r="K84" s="13" t="n">
+        <v>163636.0</v>
+      </c>
+      <c r="L84" s="13" t="n">
+        <v>16364.0</v>
+      </c>
+      <c r="M84" s="13"/>
+      <c r="N84" s="13"/>
+      <c r="O84" s="13" t="n">
+        <v>180000.0</v>
+      </c>
+      <c r="P84" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q84" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R84" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S84" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="n">
+        <v>79.0</v>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>C25TLT</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>45024</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>25/11/2025</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>3600718503</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ KINH DOANH GOLF LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H85" s="6" t="inlineStr">
+        <is>
+          <t>Số 99A, đường Phước Tân - Long Hưng, Phường Phước Tân, Tỉnh Đồng Nai, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I85" s="7" t="inlineStr">
+        <is>
+          <t>3501972322</t>
+        </is>
+      </c>
+      <c r="J85" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+        </is>
+      </c>
+      <c r="K85" s="13" t="n">
+        <v>218182.0</v>
+      </c>
+      <c r="L85" s="13" t="n">
+        <v>21818.0</v>
+      </c>
+      <c r="M85" s="13"/>
+      <c r="N85" s="13"/>
+      <c r="O85" s="13" t="n">
+        <v>240000.0</v>
+      </c>
+      <c r="P85" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q85" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R85" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S85" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="n">
+        <v>80.0</v>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>C25TLT</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>45025</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>25/11/2025</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>3600718503</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ KINH DOANH GOLF LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H86" s="6" t="inlineStr">
+        <is>
+          <t>Số 99A, đường Phước Tân - Long Hưng, Phường Phước Tân, Tỉnh Đồng Nai, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I86" s="7" t="inlineStr">
+        <is>
+          <t>3501972322</t>
+        </is>
+      </c>
+      <c r="J86" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+        </is>
+      </c>
+      <c r="K86" s="13" t="n">
+        <v>1200463.0</v>
+      </c>
+      <c r="L86" s="13" t="n">
+        <v>96037.0</v>
+      </c>
+      <c r="M86" s="13"/>
+      <c r="N86" s="13"/>
+      <c r="O86" s="13" t="n">
+        <v>1296500.0</v>
+      </c>
+      <c r="P86" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q86" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R86" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S86" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="n">
+        <v>81.0</v>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>C25TAA</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>6149</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>20/11/2025</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>3603110953</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN PHÒNG CHÁY CHỮA CHÁY TẤN ĐỨC PHÁT</t>
+        </is>
+      </c>
+      <c r="H87" s="6" t="inlineStr">
+        <is>
+          <t>Số 113/7, Tổ 1, KP 5, Đường Bùi Văn Hòa, Phường Long Bình, Tỉnh Đồng Nai, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I87" s="7" t="inlineStr">
+        <is>
+          <t>3501972322</t>
+        </is>
+      </c>
+      <c r="J87" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+        </is>
+      </c>
+      <c r="K87" s="13" t="n">
+        <v>2.44E7</v>
+      </c>
+      <c r="L87" s="13" t="n">
+        <v>1952000.0</v>
+      </c>
+      <c r="M87" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N87" s="13"/>
+      <c r="O87" s="13" t="n">
+        <v>2.6352E7</v>
+      </c>
+      <c r="P87" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q87" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R87" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S87" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="n">
+        <v>82.0</v>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>C25TAA</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>6318</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>26/11/2025</t>
+        </is>
+      </c>
+      <c r="F88" s="7" t="inlineStr">
+        <is>
+          <t>3603110953</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN PHÒNG CHÁY CHỮA CHÁY TẤN ĐỨC PHÁT</t>
+        </is>
+      </c>
+      <c r="H88" s="6" t="inlineStr">
+        <is>
+          <t>Số 113/7, Tổ 1, KP 5, Đường Bùi Văn Hòa, Phường Long Bình, Tỉnh Đồng Nai, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I88" s="7" t="inlineStr">
+        <is>
+          <t>3501972322</t>
+        </is>
+      </c>
+      <c r="J88" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+        </is>
+      </c>
+      <c r="K88" s="13" t="n">
+        <v>1.75E7</v>
+      </c>
+      <c r="L88" s="13" t="n">
+        <v>1400000.0</v>
+      </c>
+      <c r="M88" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N88" s="13"/>
+      <c r="O88" s="13" t="n">
+        <v>1.89E7</v>
+      </c>
+      <c r="P88" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q88" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R88" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S88" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="n">
+        <v>83.0</v>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>C25THT</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>05/11/2025</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>3702976581</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT THANH HÀ</t>
+        </is>
+      </c>
+      <c r="H89" s="6" t="inlineStr">
+        <is>
+          <t>Thửa đất số 112, tờ bản đồ số 8 (D4), Khu phố Bình Đáng, Phường Bình Hòa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I89" s="7" t="inlineStr">
+        <is>
+          <t>3501972322</t>
+        </is>
+      </c>
+      <c r="J89" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+        </is>
+      </c>
+      <c r="K89" s="13" t="n">
+        <v>3963000.0</v>
+      </c>
+      <c r="L89" s="13" t="n">
+        <v>317040.0</v>
+      </c>
+      <c r="M89" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N89" s="13"/>
+      <c r="O89" s="13" t="n">
+        <v>4280040.0</v>
+      </c>
+      <c r="P89" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q89" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R89" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S89" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="n">
+        <v>84.0</v>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>C25TAA</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>1293</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>18/11/2025</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>3703359895</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH TMDV HOA BÁCH HỢP</t>
+        </is>
+      </c>
+      <c r="H90" s="6" t="inlineStr">
+        <is>
+          <t>Số 210 Đường tỉnh 746, Tổ 4, Khu phố Tân Bình, Phường Tân Hiệp, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="I90" s="7" t="inlineStr">
+        <is>
+          <t>3501972322</t>
+        </is>
+      </c>
+      <c r="J90" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ PHÒNG CHÁY CHỮA CHÁY MINH HOÀNG</t>
+        </is>
+      </c>
+      <c r="K90" s="13" t="n">
+        <v>1800000.0</v>
+      </c>
+      <c r="L90" s="13" t="n">
+        <v>144000.0</v>
+      </c>
+      <c r="M90" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N90" s="13"/>
+      <c r="O90" s="13" t="n">
+        <v>1944000.0</v>
+      </c>
+      <c r="P90" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q90" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R90" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S90" s="6" t="inlineStr">
         <is>
           <t>Đã cấp mã hóa đơn</t>
         </is>
